--- a/Design Files/BLE_product-v1.0/BOM/eSpark_BOM_BLE_product-v1.0.xlsx
+++ b/Design Files/BLE_product-v1.0/BOM/eSpark_BOM_BLE_product-v1.0.xlsx
@@ -9,17 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="20 Boards" sheetId="2" r:id="rId2"/>
+    <sheet name="50 Boards" sheetId="3" r:id="rId3"/>
+    <sheet name="100 Boards" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="207">
   <si>
     <t>Component list</t>
   </si>
@@ -450,9 +453,6 @@
     <t>C315248</t>
   </si>
   <si>
-    <t>C109447</t>
-  </si>
-  <si>
     <t>C605210</t>
   </si>
   <si>
@@ -595,6 +595,54 @@
   </si>
   <si>
     <t>JTAG</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>CL10A226MP8NUNE</t>
+  </si>
+  <si>
+    <t>C86295</t>
+  </si>
+  <si>
+    <t>Quantity (10 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MOQ (10 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (20 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MOQ (20 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (20 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (20 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (10 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (10 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (50 Boards)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MOQ (50 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (50 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (50 Boards)</t>
   </si>
 </sst>
 </file>
@@ -606,7 +654,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -758,6 +806,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -785,7 +858,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1045,11 +1118,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1242,8 +1327,39 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1307,6 +1423,168 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29927550" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19545300" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19545300" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19545300" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1591,10 +1869,10 @@
     <col min="4" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1636,7 +1914,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1661,7 +1939,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1686,7 +1964,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1814,37 +2092,37 @@
         <v>124</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J9" s="30" t="s">
         <v>140</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="N9" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="O9" s="30" t="s">
-        <v>181</v>
-      </c>
       <c r="P9" s="30" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="Q9" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="R9" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>184</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1871,26 +2149,34 @@
       <c r="H10" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I10" s="37"/>
+      <c r="I10" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J10" s="37" t="s">
         <v>141</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L10" s="37">
         <v>6</v>
       </c>
       <c r="M10" s="37">
-        <f>L10*5</f>
-        <v>30</v>
-      </c>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="38"/>
+        <f>L10*10</f>
+        <v>60</v>
+      </c>
+      <c r="N10" s="37">
+        <v>100</v>
+      </c>
+      <c r="O10" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="50"/>
@@ -1919,26 +2205,34 @@
       <c r="H11" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="51"/>
+      <c r="I11" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J11" s="51" t="s">
         <v>142</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
       </c>
-      <c r="M11" s="51">
-        <f t="shared" ref="M11" si="1">L11*5</f>
-        <v>5</v>
-      </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="52"/>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M38" si="1">L11*10</f>
+        <v>10</v>
+      </c>
+      <c r="N11" s="51">
+        <v>50</v>
+      </c>
+      <c r="O11" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="52">
+        <v>1.09E-2</v>
+      </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
-        <v>0</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -1961,32 +2255,40 @@
       <c r="F12" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="76" t="s">
         <v>104</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I12" s="37"/>
+      <c r="I12" s="37" t="s">
+        <v>193</v>
+      </c>
       <c r="J12" s="37" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
       </c>
       <c r="M12" s="37">
-        <f>L12*5</f>
-        <v>5</v>
-      </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N12" s="37">
+        <v>50</v>
+      </c>
+      <c r="O12" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.35E-2</v>
+      </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>0</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
@@ -2015,26 +2317,34 @@
       <c r="H13" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="I13" s="51"/>
+      <c r="I13" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J13" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
       </c>
-      <c r="M13" s="51">
-        <f t="shared" ref="M13" si="3">L13*5</f>
-        <v>5</v>
-      </c>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="52"/>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N13" s="51">
+        <v>100</v>
+      </c>
+      <c r="O13" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="52">
+        <v>5.3E-3</v>
+      </c>
       <c r="Q13" s="52">
-        <f t="shared" ref="Q13" si="4">P13*N13</f>
-        <v>0</v>
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>0.53</v>
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
@@ -2063,26 +2373,34 @@
       <c r="H14" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I14" s="37"/>
+      <c r="I14" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J14" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
       </c>
       <c r="M14" s="37">
-        <f>L14*5</f>
-        <v>5</v>
-      </c>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N14" s="37">
+        <v>20</v>
+      </c>
+      <c r="O14" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="38">
+        <v>3.44E-2</v>
+      </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -2103,7 +2421,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>82</v>
@@ -2111,26 +2429,34 @@
       <c r="H15" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="I15" s="51"/>
+      <c r="I15" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J15" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
       </c>
-      <c r="M15" s="51">
-        <f t="shared" ref="M15" si="5">L15*5</f>
-        <v>5</v>
-      </c>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="52"/>
+      <c r="M15" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N15" s="51">
+        <v>11</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="52">
+        <v>0.50600000000000001</v>
+      </c>
       <c r="Q15" s="52">
-        <f t="shared" ref="Q15" si="6">P15*N15</f>
-        <v>0</v>
+        <f t="shared" ref="Q15" si="4">P15*N15</f>
+        <v>5.5659999999999998</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
@@ -2159,26 +2485,34 @@
       <c r="H16" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I16" s="37"/>
+      <c r="I16" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J16" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
       </c>
       <c r="M16" s="37">
-        <f>L16*5</f>
-        <v>5</v>
-      </c>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N16" s="37">
+        <v>20</v>
+      </c>
+      <c r="O16" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="38">
+        <v>6.3100000000000003E-2</v>
+      </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>0</v>
+        <v>1.262</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
@@ -2189,41 +2523,52 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="51" t="s">
+      <c r="D17" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="51" t="s">
+      <c r="E17" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51">
+      <c r="H17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73">
         <v>4</v>
       </c>
-      <c r="M17" s="51">
-        <f t="shared" ref="M17" si="7">L17*5</f>
-        <v>20</v>
-      </c>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52">
-        <f t="shared" ref="Q17" si="8">P17*N17</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="51"/>
-      <c r="S17" s="59"/>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R17" s="73"/>
+      <c r="S17" s="75"/>
     </row>
     <row r="18" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -2256,8 +2601,8 @@
         <v>1</v>
       </c>
       <c r="M18" s="37">
-        <f>L18*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="N18" s="37"/>
       <c r="O18" s="37"/>
@@ -2275,38 +2620,51 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="D19" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="51" t="s">
+      <c r="F19" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="51" t="s">
+      <c r="G19" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51">
-        <v>1</v>
-      </c>
-      <c r="M19" s="51">
-        <f t="shared" ref="M19" si="9">L19*5</f>
-        <v>5</v>
-      </c>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="52">
-        <f t="shared" ref="Q19" si="10">P19*N19</f>
-        <v>0</v>
+      <c r="H19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19" s="73">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q19" s="74" t="s">
+        <v>189</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -2317,41 +2675,52 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="F20" s="37" t="s">
+      <c r="E20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37">
-        <v>1</v>
-      </c>
-      <c r="M20" s="37">
-        <f>L20*5</f>
-        <v>5</v>
-      </c>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38">
-        <f>P20*N20</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="37"/>
-      <c r="S20" s="59"/>
+      <c r="G20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" s="76">
+        <v>1</v>
+      </c>
+      <c r="M20" s="76">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="O20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="R20" s="76"/>
+      <c r="S20" s="75"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -2377,26 +2746,34 @@
       <c r="H21" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="I21" s="51"/>
+      <c r="I21" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J21" s="51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
       </c>
-      <c r="M21" s="51">
-        <f t="shared" ref="M21" si="11">L21*5</f>
-        <v>5</v>
-      </c>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="52"/>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N21" s="51">
+        <v>15</v>
+      </c>
+      <c r="O21" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P21" s="52">
+        <v>8.4000000000000005E-2</v>
+      </c>
       <c r="Q21" s="52">
-        <f t="shared" ref="Q21" si="12">P21*N21</f>
-        <v>0</v>
+        <f t="shared" ref="Q21" si="5">P21*N21</f>
+        <v>1.26</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
@@ -2417,7 +2794,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>88</v>
@@ -2425,24 +2802,34 @@
       <c r="H22" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="I22" s="37"/>
+      <c r="I22" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J22" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="K22" s="37"/>
+        <v>148</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="L22" s="37">
         <v>1</v>
       </c>
       <c r="M22" s="37">
-        <f>L22*5</f>
-        <v>5</v>
-      </c>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N22" s="37">
+        <v>20</v>
+      </c>
+      <c r="O22" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="38">
+        <v>5.6099999999999997E-2</v>
+      </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0</v>
+        <v>1.1219999999999999</v>
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
@@ -2471,24 +2858,32 @@
       <c r="H23" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="I23" s="51"/>
+      <c r="I23" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J23" s="51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K23" s="51"/>
       <c r="L23" s="51">
         <v>1</v>
       </c>
-      <c r="M23" s="51">
-        <f t="shared" ref="M23" si="13">L23*5</f>
-        <v>5</v>
-      </c>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="52"/>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N23" s="51">
+        <v>20</v>
+      </c>
+      <c r="O23" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P23" s="52">
+        <v>3.3500000000000002E-2</v>
+      </c>
       <c r="Q23" s="52">
-        <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>0</v>
+        <f t="shared" ref="Q23" si="6">P23*N23</f>
+        <v>0.67</v>
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
@@ -2517,26 +2912,34 @@
       <c r="H24" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I24" s="37"/>
+      <c r="I24" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J24" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L24" s="37">
         <v>5</v>
       </c>
       <c r="M24" s="37">
-        <f>L24*5</f>
-        <v>25</v>
-      </c>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="38"/>
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N24" s="37">
+        <v>100</v>
+      </c>
+      <c r="O24" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P24" s="38">
+        <v>8.0000000000000004E-4</v>
+      </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -2565,26 +2968,34 @@
       <c r="H25" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="51"/>
+      <c r="I25" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J25" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
       </c>
-      <c r="M25" s="51">
-        <f t="shared" ref="M25" si="15">L25*5</f>
-        <v>5</v>
-      </c>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="52"/>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N25" s="51">
+        <v>100</v>
+      </c>
+      <c r="O25" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="52">
+        <v>8.0000000000000004E-4</v>
+      </c>
       <c r="Q25" s="52">
-        <f t="shared" ref="Q25" si="16">P25*N25</f>
-        <v>0</v>
+        <f t="shared" ref="Q25" si="7">P25*N25</f>
+        <v>0.08</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -2613,26 +3024,34 @@
       <c r="H26" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="I26" s="37"/>
+      <c r="I26" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J26" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
       </c>
       <c r="M26" s="37">
-        <f>L26*5</f>
-        <v>5</v>
-      </c>
-      <c r="N26" s="37"/>
-      <c r="O26" s="37"/>
-      <c r="P26" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P26" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>0</v>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
@@ -2661,26 +3080,34 @@
       <c r="H27" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="I27" s="51"/>
+      <c r="I27" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J27" s="51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L27" s="51">
         <v>2</v>
       </c>
-      <c r="M27" s="51">
-        <f t="shared" ref="M27" si="17">L27*5</f>
-        <v>10</v>
-      </c>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="52"/>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N27" s="51">
+        <v>50</v>
+      </c>
+      <c r="O27" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P27" s="52">
+        <v>4.5999999999999999E-3</v>
+      </c>
       <c r="Q27" s="52">
-        <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>0</v>
+        <f t="shared" ref="Q27" si="8">P27*N27</f>
+        <v>0.22999999999999998</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
@@ -2709,26 +3136,34 @@
       <c r="H28" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="I28" s="37"/>
+      <c r="I28" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J28" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L28" s="37">
         <v>4</v>
       </c>
       <c r="M28" s="37">
-        <f>L28*5</f>
-        <v>20</v>
-      </c>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="38"/>
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N28" s="37">
+        <v>100</v>
+      </c>
+      <c r="O28" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P28" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
@@ -2757,24 +3192,34 @@
       <c r="H29" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="I29" s="51"/>
+      <c r="I29" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J29" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="K29" s="51"/>
+        <v>155</v>
+      </c>
+      <c r="K29" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="L29" s="51">
         <v>1</v>
       </c>
-      <c r="M29" s="51">
-        <f t="shared" ref="M29" si="19">L29*5</f>
-        <v>5</v>
-      </c>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="52"/>
+      <c r="M29" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N29" s="51">
+        <v>15</v>
+      </c>
+      <c r="O29" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P29" s="52">
+        <v>0.2923</v>
+      </c>
       <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="20">P29*N29</f>
-        <v>0</v>
+        <f t="shared" ref="Q29" si="9">P29*N29</f>
+        <v>4.3845000000000001</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
@@ -2803,24 +3248,34 @@
       <c r="H30" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="I30" s="37"/>
+      <c r="I30" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J30" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="K30" s="37"/>
+        <v>156</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="L30" s="37">
         <v>1</v>
       </c>
       <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>5</v>
-      </c>
-      <c r="N30" s="37"/>
-      <c r="O30" s="37"/>
-      <c r="P30" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N30" s="37">
+        <v>11</v>
+      </c>
+      <c r="O30" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P30" s="38">
+        <v>0.87819999999999998</v>
+      </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>0</v>
+        <v>9.6601999999999997</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
@@ -2849,23 +3304,25 @@
       <c r="H31" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="I31" s="51"/>
+      <c r="I31" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J31" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K31" s="51"/>
       <c r="L31" s="51">
         <v>1</v>
       </c>
-      <c r="M31" s="51">
-        <f t="shared" ref="M31" si="21">L31*5</f>
-        <v>5</v>
+      <c r="M31" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="N31" s="51"/>
       <c r="O31" s="51"/>
       <c r="P31" s="52"/>
       <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="22">P31*N31</f>
+        <f t="shared" ref="Q31" si="10">P31*N31</f>
         <v>0</v>
       </c>
       <c r="R31" s="51"/>
@@ -2895,24 +3352,32 @@
       <c r="H32" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="I32" s="37"/>
+      <c r="I32" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J32" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K32" s="37"/>
       <c r="L32" s="37">
         <v>1</v>
       </c>
       <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="37"/>
-      <c r="O32" s="37"/>
-      <c r="P32" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N32" s="37">
+        <v>15</v>
+      </c>
+      <c r="O32" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P32" s="38">
+        <v>7.9299999999999995E-2</v>
+      </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>0</v>
+        <v>1.1895</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
@@ -2936,29 +3401,37 @@
         <v>95</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H33" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="I33" s="51"/>
+      <c r="I33" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J33" s="51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K33" s="51"/>
       <c r="L33" s="51">
         <v>1</v>
       </c>
-      <c r="M33" s="51">
-        <f t="shared" ref="M33" si="23">L33*5</f>
-        <v>5</v>
-      </c>
-      <c r="N33" s="51"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="52"/>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N33" s="51">
+        <v>11</v>
+      </c>
+      <c r="O33" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P33" s="52">
+        <v>0.6794</v>
+      </c>
       <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
-        <v>0</v>
+        <f t="shared" ref="Q33" si="11">P33*N33</f>
+        <v>7.4733999999999998</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
@@ -2987,24 +3460,32 @@
       <c r="H34" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="I34" s="37"/>
+      <c r="I34" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J34" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K34" s="37"/>
       <c r="L34" s="37">
         <v>1</v>
       </c>
       <c r="M34" s="37">
-        <f>L34*5</f>
-        <v>5</v>
-      </c>
-      <c r="N34" s="37"/>
-      <c r="O34" s="37"/>
-      <c r="P34" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N34" s="37">
+        <v>15</v>
+      </c>
+      <c r="O34" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.1444</v>
+      </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>0</v>
+        <v>2.1659999999999999</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
@@ -3033,21 +3514,23 @@
       <c r="H35" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="I35" s="51"/>
+      <c r="I35" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="J35" s="51"/>
       <c r="K35" s="51"/>
       <c r="L35" s="51">
         <v>1</v>
       </c>
-      <c r="M35" s="51">
-        <f t="shared" ref="M35" si="25">L35*5</f>
-        <v>5</v>
+      <c r="M35" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="N35" s="51"/>
       <c r="O35" s="51"/>
       <c r="P35" s="52"/>
       <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="26">P35*N35</f>
+        <f t="shared" ref="Q35" si="12">P35*N35</f>
         <v>0</v>
       </c>
       <c r="R35" s="51"/>
@@ -3077,24 +3560,32 @@
       <c r="H36" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="I36" s="37"/>
+      <c r="I36" s="37" t="s">
+        <v>189</v>
+      </c>
       <c r="J36" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K36" s="37"/>
       <c r="L36" s="37">
         <v>1</v>
       </c>
       <c r="M36" s="37">
-        <f>L36*5</f>
-        <v>5</v>
-      </c>
-      <c r="N36" s="37"/>
-      <c r="O36" s="37"/>
-      <c r="P36" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N36" s="37">
+        <v>11</v>
+      </c>
+      <c r="O36" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P36" s="38">
+        <v>0.33260000000000001</v>
+      </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>0</v>
+        <v>3.6585999999999999</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
@@ -3125,22 +3616,28 @@
       </c>
       <c r="I37" s="51"/>
       <c r="J37" s="51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K37" s="51"/>
       <c r="L37" s="51">
         <v>1</v>
       </c>
-      <c r="M37" s="51">
-        <f t="shared" ref="M37" si="27">L37*5</f>
-        <v>5</v>
-      </c>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="52"/>
+      <c r="M37" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N37" s="51">
+        <v>11</v>
+      </c>
+      <c r="O37" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P37" s="52">
+        <v>2.1604999999999999</v>
+      </c>
       <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="28">P37*N37</f>
-        <v>0</v>
+        <f t="shared" ref="Q37" si="13">P37*N37</f>
+        <v>23.765499999999999</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
@@ -3171,22 +3668,28 @@
       </c>
       <c r="I38" s="37"/>
       <c r="J38" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K38" s="37"/>
       <c r="L38" s="37">
         <v>1</v>
       </c>
       <c r="M38" s="37">
-        <f>L38*5</f>
-        <v>5</v>
-      </c>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="38"/>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N38" s="37">
+        <v>11</v>
+      </c>
+      <c r="O38" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P38" s="38">
+        <v>1.3826000000000001</v>
+      </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>0</v>
+        <v>15.208600000000001</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
@@ -3210,9 +3713,9 @@
       </c>
       <c r="O39" s="69"/>
       <c r="P39" s="69"/>
-      <c r="Q39" s="48" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
+      <c r="Q39" s="48">
+        <f>SUM(Q10:Q38)</f>
+        <v>80.484300000000005</v>
       </c>
       <c r="R39" s="64"/>
       <c r="S39" s="65"/>
@@ -3236,9 +3739,9 @@
       </c>
       <c r="O40" s="69"/>
       <c r="P40" s="69"/>
-      <c r="Q40" s="49" t="e">
-        <f>Q39/5</f>
-        <v>#REF!</v>
+      <c r="Q40" s="49">
+        <f>Q39/10</f>
+        <v>8.0484299999999998</v>
       </c>
       <c r="R40" s="66"/>
       <c r="S40" s="67"/>
@@ -3251,8 +3754,5790 @@
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="N40:P40"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O21" r:id="rId7"/>
+    <hyperlink ref="O22" r:id="rId8"/>
+    <hyperlink ref="O23" r:id="rId9"/>
+    <hyperlink ref="O24" r:id="rId10"/>
+    <hyperlink ref="O25" r:id="rId11"/>
+    <hyperlink ref="O26" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O28" r:id="rId14"/>
+    <hyperlink ref="O29" r:id="rId15"/>
+    <hyperlink ref="O30" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O34" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O12" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <drawing r:id="rId25"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="61"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="62"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="63"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="63"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="63"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="63"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="63"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*20</f>
+        <v>120</v>
+      </c>
+      <c r="N10" s="37">
+        <v>200</v>
+      </c>
+      <c r="O10" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.22</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="50"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="L11" s="51">
+        <v>1</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M38" si="1">L11*20</f>
+        <v>20</v>
+      </c>
+      <c r="N11" s="51">
+        <v>50</v>
+      </c>
+      <c r="O11" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="52">
+        <v>1.09E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N12" s="37">
+        <v>50</v>
+      </c>
+      <c r="O12" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.35E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N13" s="51">
+        <v>100</v>
+      </c>
+      <c r="O13" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="52">
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>0.53</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N14" s="37">
+        <v>40</v>
+      </c>
+      <c r="O14" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="38">
+        <v>3.44E-2</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>1.3759999999999999</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L15" s="51">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N15" s="51">
+        <v>21</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="52">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="Q15" s="52">
+        <f t="shared" ref="Q15" si="4">P15*N15</f>
+        <v>10.625999999999999</v>
+      </c>
+      <c r="R15" s="51"/>
+      <c r="S15" s="59"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N16" s="37">
+        <v>30</v>
+      </c>
+      <c r="O16" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="38">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>1.893</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73">
+        <v>4</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R17" s="73"/>
+      <c r="S17" s="75"/>
+    </row>
+    <row r="18" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19" s="73">
+        <v>1</v>
+      </c>
+      <c r="M19" s="73">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="79" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" s="76">
+        <v>1</v>
+      </c>
+      <c r="M20" s="76">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="O20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="R20" s="76"/>
+      <c r="S20" s="75"/>
+    </row>
+    <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N21" s="51">
+        <v>25</v>
+      </c>
+      <c r="O21" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P21" s="52">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="5">P21*N21</f>
+        <v>2.1</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N22" s="37">
+        <v>30</v>
+      </c>
+      <c r="O22" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="38">
+        <v>5.6099999999999997E-2</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>1.6829999999999998</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N23" s="51">
+        <v>40</v>
+      </c>
+      <c r="O23" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P23" s="52">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="6">P23*N23</f>
+        <v>1.34</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" s="37">
+        <v>5</v>
+      </c>
+      <c r="M24" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N24" s="37">
+        <v>200</v>
+      </c>
+      <c r="O24" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P24" s="38">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>0.16</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="59"/>
+    </row>
+    <row r="25" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="51">
+        <v>1</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N25" s="51">
+        <v>100</v>
+      </c>
+      <c r="O25" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="52">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25" si="7">P25*N25</f>
+        <v>0.08</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="59"/>
+    </row>
+    <row r="26" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="L26" s="37">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P26" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="59"/>
+    </row>
+    <row r="27" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="47">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="51">
+        <v>2</v>
+      </c>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N27" s="51">
+        <v>50</v>
+      </c>
+      <c r="O27" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P27" s="52">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="52">
+        <f t="shared" ref="Q27" si="8">P27*N27</f>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="R27" s="51"/>
+      <c r="S27" s="59"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="37">
+        <v>4</v>
+      </c>
+      <c r="M28" s="37">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N28" s="37">
+        <v>100</v>
+      </c>
+      <c r="O28" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P28" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.09</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="59"/>
+    </row>
+    <row r="29" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="47">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="L29" s="51">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N29" s="51">
+        <v>25</v>
+      </c>
+      <c r="O29" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P29" s="52">
+        <v>0.2923</v>
+      </c>
+      <c r="Q29" s="52">
+        <f t="shared" ref="Q29" si="9">P29*N29</f>
+        <v>7.3075000000000001</v>
+      </c>
+      <c r="R29" s="51"/>
+      <c r="S29" s="59"/>
+    </row>
+    <row r="30" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L30" s="37">
+        <v>1</v>
+      </c>
+      <c r="M30" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N30" s="37">
+        <v>21</v>
+      </c>
+      <c r="O30" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P30" s="38">
+        <v>0.73980000000000001</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>15.5358</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="59"/>
+    </row>
+    <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="47">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="I31" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52">
+        <f t="shared" ref="Q31" si="10">P31*N31</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="51"/>
+      <c r="S31" s="59"/>
+    </row>
+    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N32" s="37">
+        <v>25</v>
+      </c>
+      <c r="O32" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P32" s="38">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>1.9824999999999999</v>
+      </c>
+      <c r="R32" s="37"/>
+      <c r="S32" s="59"/>
+    </row>
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="47">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J33" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N33" s="51">
+        <v>21</v>
+      </c>
+      <c r="O33" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P33" s="52">
+        <v>0.6794</v>
+      </c>
+      <c r="Q33" s="52">
+        <f t="shared" ref="Q33" si="11">P33*N33</f>
+        <v>14.2674</v>
+      </c>
+      <c r="R33" s="51"/>
+      <c r="S33" s="59"/>
+    </row>
+    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N34" s="37">
+        <v>25</v>
+      </c>
+      <c r="O34" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.1444</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>3.61</v>
+      </c>
+      <c r="R34" s="37"/>
+      <c r="S34" s="59"/>
+    </row>
+    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="47">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52">
+        <f t="shared" ref="Q35" si="12">P35*N35</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="51"/>
+      <c r="S35" s="59"/>
+    </row>
+    <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="46">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N36" s="37">
+        <v>21</v>
+      </c>
+      <c r="O36" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P36" s="38">
+        <v>0.33260000000000001</v>
+      </c>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
+        <v>6.9846000000000004</v>
+      </c>
+      <c r="R36" s="37"/>
+      <c r="S36" s="59"/>
+    </row>
+    <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="47">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="K37" s="51"/>
+      <c r="L37" s="51">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N37" s="51">
+        <v>21</v>
+      </c>
+      <c r="O37" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P37" s="52">
+        <v>2.1604999999999999</v>
+      </c>
+      <c r="Q37" s="52">
+        <f t="shared" ref="Q37" si="13">P37*N37</f>
+        <v>45.3705</v>
+      </c>
+      <c r="R37" s="51"/>
+      <c r="S37" s="59"/>
+    </row>
+    <row r="38" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="46">
+        <f>ROW(B38) - ROW($B$9)</f>
+        <v>29</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37">
+        <v>1</v>
+      </c>
+      <c r="M38" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N38" s="37">
+        <v>21</v>
+      </c>
+      <c r="O38" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P38" s="38">
+        <v>1.3826000000000001</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>29.034600000000001</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="O39" s="69"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="48">
+        <f>SUM(Q10:Q38)</f>
+        <v>145.71090000000001</v>
+      </c>
+      <c r="R39" s="64"/>
+      <c r="S39" s="65"/>
+    </row>
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="O40" s="69"/>
+      <c r="P40" s="69"/>
+      <c r="Q40" s="49">
+        <f>Q39/20</f>
+        <v>7.2855450000000008</v>
+      </c>
+      <c r="R40" s="66"/>
+      <c r="S40" s="67"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S40"/>
+    <mergeCell ref="N40:P40"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O21" r:id="rId7"/>
+    <hyperlink ref="O22" r:id="rId8"/>
+    <hyperlink ref="O23" r:id="rId9"/>
+    <hyperlink ref="O24" r:id="rId10"/>
+    <hyperlink ref="O25" r:id="rId11"/>
+    <hyperlink ref="O26" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O28" r:id="rId14"/>
+    <hyperlink ref="O29" r:id="rId15"/>
+    <hyperlink ref="O30" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O34" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O12" r:id="rId23"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId24"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="61"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="62"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="63"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="63"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="63"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="63"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="63"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*50</f>
+        <v>300</v>
+      </c>
+      <c r="N10" s="37">
+        <v>400</v>
+      </c>
+      <c r="O10" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.44</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="50"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="L11" s="51">
+        <v>1</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M38" si="1">L11*50</f>
+        <v>50</v>
+      </c>
+      <c r="N11" s="51">
+        <v>100</v>
+      </c>
+      <c r="O11" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="52">
+        <v>1.09E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N12" s="37">
+        <v>100</v>
+      </c>
+      <c r="O12" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.35E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>1.35</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N13" s="51">
+        <v>100</v>
+      </c>
+      <c r="O13" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="52">
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>0.53</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N14" s="37">
+        <v>60</v>
+      </c>
+      <c r="O14" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="38">
+        <v>3.44E-2</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>2.0640000000000001</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L15" s="51">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N15" s="51">
+        <v>51</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="52">
+        <v>0.45979999999999999</v>
+      </c>
+      <c r="Q15" s="52">
+        <f t="shared" ref="Q15" si="4">P15*N15</f>
+        <v>23.4498</v>
+      </c>
+      <c r="R15" s="51"/>
+      <c r="S15" s="59"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N16" s="37">
+        <v>60</v>
+      </c>
+      <c r="O16" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="38">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>3.786</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="L17" s="73">
+        <v>4</v>
+      </c>
+      <c r="M17" s="73">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="N17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R17" s="73"/>
+      <c r="S17" s="75"/>
+    </row>
+    <row r="18" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19" s="73">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" s="76">
+        <v>1</v>
+      </c>
+      <c r="M20" s="76">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="O20" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="R20" s="76"/>
+      <c r="S20" s="75"/>
+    </row>
+    <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N21" s="51">
+        <v>55</v>
+      </c>
+      <c r="O21" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P21" s="52">
+        <v>7.0699999999999999E-2</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="5">P21*N21</f>
+        <v>3.8885000000000001</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N22" s="37">
+        <v>10</v>
+      </c>
+      <c r="O22" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="38">
+        <v>5.6099999999999997E-2</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.56099999999999994</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N23" s="51">
+        <v>20</v>
+      </c>
+      <c r="O23" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P23" s="52">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="6">P23*N23</f>
+        <v>0.67</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" s="37">
+        <v>5</v>
+      </c>
+      <c r="M24" s="37">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="N24" s="37">
+        <v>100</v>
+      </c>
+      <c r="O24" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P24" s="38">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>0.08</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="59"/>
+    </row>
+    <row r="25" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="51">
+        <v>1</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N25" s="51">
+        <v>100</v>
+      </c>
+      <c r="O25" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="52">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25" si="7">P25*N25</f>
+        <v>0.08</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="59"/>
+    </row>
+    <row r="26" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="L26" s="37">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P26" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="59"/>
+    </row>
+    <row r="27" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="47">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="51">
+        <v>2</v>
+      </c>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N27" s="51">
+        <v>50</v>
+      </c>
+      <c r="O27" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P27" s="52">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="52">
+        <f t="shared" ref="Q27" si="8">P27*N27</f>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="R27" s="51"/>
+      <c r="S27" s="59"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="37">
+        <v>4</v>
+      </c>
+      <c r="M28" s="37">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="N28" s="37">
+        <v>100</v>
+      </c>
+      <c r="O28" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P28" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.09</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="59"/>
+    </row>
+    <row r="29" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="47">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="L29" s="51">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N29" s="51">
+        <v>10</v>
+      </c>
+      <c r="O29" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P29" s="52">
+        <v>0.2923</v>
+      </c>
+      <c r="Q29" s="52">
+        <f t="shared" ref="Q29" si="9">P29*N29</f>
+        <v>2.923</v>
+      </c>
+      <c r="R29" s="51"/>
+      <c r="S29" s="59"/>
+    </row>
+    <row r="30" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L30" s="37">
+        <v>1</v>
+      </c>
+      <c r="M30" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N30" s="37">
+        <v>6</v>
+      </c>
+      <c r="O30" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P30" s="38">
+        <v>0.87819999999999998</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>5.2691999999999997</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="59"/>
+    </row>
+    <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="47">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="I31" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52">
+        <f t="shared" ref="Q31" si="10">P31*N31</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="51"/>
+      <c r="S31" s="59"/>
+    </row>
+    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N32" s="37">
+        <v>10</v>
+      </c>
+      <c r="O32" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P32" s="38">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>0.79299999999999993</v>
+      </c>
+      <c r="R32" s="37"/>
+      <c r="S32" s="59"/>
+    </row>
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="47">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J33" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N33" s="51">
+        <v>6</v>
+      </c>
+      <c r="O33" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P33" s="52">
+        <v>0.81779999999999997</v>
+      </c>
+      <c r="Q33" s="52">
+        <f t="shared" ref="Q33" si="11">P33*N33</f>
+        <v>4.9067999999999996</v>
+      </c>
+      <c r="R33" s="51"/>
+      <c r="S33" s="59"/>
+    </row>
+    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N34" s="37">
+        <v>10</v>
+      </c>
+      <c r="O34" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.1444</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>1.444</v>
+      </c>
+      <c r="R34" s="37"/>
+      <c r="S34" s="59"/>
+    </row>
+    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="47">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52">
+        <f t="shared" ref="Q35" si="12">P35*N35</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="51"/>
+      <c r="S35" s="59"/>
+    </row>
+    <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="46">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N36" s="37">
+        <v>6</v>
+      </c>
+      <c r="O36" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P36" s="38">
+        <v>0.33260000000000001</v>
+      </c>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
+        <v>1.9956</v>
+      </c>
+      <c r="R36" s="37"/>
+      <c r="S36" s="59"/>
+    </row>
+    <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="47">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="K37" s="51"/>
+      <c r="L37" s="51">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N37" s="51">
+        <v>6</v>
+      </c>
+      <c r="O37" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P37" s="52">
+        <v>2.3832</v>
+      </c>
+      <c r="Q37" s="52">
+        <f t="shared" ref="Q37" si="13">P37*N37</f>
+        <v>14.299199999999999</v>
+      </c>
+      <c r="R37" s="51"/>
+      <c r="S37" s="59"/>
+    </row>
+    <row r="38" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="46">
+        <f>ROW(B38) - ROW($B$9)</f>
+        <v>29</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37">
+        <v>1</v>
+      </c>
+      <c r="M38" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N38" s="37">
+        <v>6</v>
+      </c>
+      <c r="O38" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P38" s="38">
+        <v>1.6069</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>9.6414000000000009</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="O39" s="69"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="48">
+        <f>SUM(Q10:Q38)</f>
+        <v>79.651499999999999</v>
+      </c>
+      <c r="R39" s="64"/>
+      <c r="S39" s="65"/>
+    </row>
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="O40" s="69"/>
+      <c r="P40" s="69"/>
+      <c r="Q40" s="49">
+        <f>Q39/5</f>
+        <v>15.930299999999999</v>
+      </c>
+      <c r="R40" s="66"/>
+      <c r="S40" s="67"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S40"/>
+    <mergeCell ref="N40:P40"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O21" r:id="rId7"/>
+    <hyperlink ref="O22" r:id="rId8"/>
+    <hyperlink ref="O23" r:id="rId9"/>
+    <hyperlink ref="O24" r:id="rId10"/>
+    <hyperlink ref="O25" r:id="rId11"/>
+    <hyperlink ref="O26" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O28" r:id="rId14"/>
+    <hyperlink ref="O29" r:id="rId15"/>
+    <hyperlink ref="O30" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O34" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O12" r:id="rId23"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId24"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="61"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="62"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="63"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="63"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="63"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="63"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="63"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*5</f>
+        <v>30</v>
+      </c>
+      <c r="N10" s="37">
+        <v>100</v>
+      </c>
+      <c r="O10" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.11</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="50"/>
+    </row>
+    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="47">
+        <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="L11" s="51">
+        <v>1</v>
+      </c>
+      <c r="M11" s="51">
+        <f t="shared" ref="M11" si="1">L11*5</f>
+        <v>5</v>
+      </c>
+      <c r="N11" s="51">
+        <v>50</v>
+      </c>
+      <c r="O11" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="52">
+        <v>1.09E-2</v>
+      </c>
+      <c r="Q11" s="52">
+        <f t="shared" ref="Q11" si="2">P11*N11</f>
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+    </row>
+    <row r="12" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="46">
+        <f>ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="L12" s="37">
+        <v>1</v>
+      </c>
+      <c r="M12" s="37">
+        <f>L12*5</f>
+        <v>5</v>
+      </c>
+      <c r="N12" s="37">
+        <v>50</v>
+      </c>
+      <c r="O12" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.35E-2</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="59"/>
+    </row>
+    <row r="13" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="47">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="K13" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
+      </c>
+      <c r="M13" s="51">
+        <f t="shared" ref="M13" si="3">L13*5</f>
+        <v>5</v>
+      </c>
+      <c r="N13" s="51">
+        <v>100</v>
+      </c>
+      <c r="O13" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="52">
+        <v>5.3E-3</v>
+      </c>
+      <c r="Q13" s="52">
+        <f t="shared" ref="Q13" si="4">P13*N13</f>
+        <v>0.53</v>
+      </c>
+      <c r="R13" s="51"/>
+      <c r="S13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="46">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" s="37">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f>L14*5</f>
+        <v>5</v>
+      </c>
+      <c r="N14" s="37">
+        <v>20</v>
+      </c>
+      <c r="O14" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="38">
+        <v>3.44E-2</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="47">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L15" s="51">
+        <v>1</v>
+      </c>
+      <c r="M15" s="51">
+        <f t="shared" ref="M15" si="5">L15*5</f>
+        <v>5</v>
+      </c>
+      <c r="N15" s="51">
+        <v>6</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="52">
+        <v>0.5998</v>
+      </c>
+      <c r="Q15" s="52">
+        <f t="shared" ref="Q15" si="6">P15*N15</f>
+        <v>3.5987999999999998</v>
+      </c>
+      <c r="R15" s="51"/>
+      <c r="S15" s="59"/>
+    </row>
+    <row r="16" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="46">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="L16" s="37">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f>L16*5</f>
+        <v>5</v>
+      </c>
+      <c r="N16" s="37">
+        <v>10</v>
+      </c>
+      <c r="O16" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="38">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="Q16" s="38">
+        <f>P16*N16</f>
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="R16" s="37"/>
+      <c r="S16" s="59"/>
+    </row>
+    <row r="17" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="47">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73">
+        <v>4</v>
+      </c>
+      <c r="M17" s="73">
+        <f t="shared" ref="M17" si="7">L17*5</f>
+        <v>20</v>
+      </c>
+      <c r="N17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O17" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q17" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R17" s="73"/>
+      <c r="S17" s="75"/>
+    </row>
+    <row r="18" spans="1:19" ht="84" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="46">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f>L18*5</f>
+        <v>5</v>
+      </c>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="59"/>
+    </row>
+    <row r="19" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="L19" s="73">
+        <v>1</v>
+      </c>
+      <c r="M19" s="73">
+        <f t="shared" ref="M19" si="8">L19*5</f>
+        <v>5</v>
+      </c>
+      <c r="N19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="O19" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="P19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q19" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="R19" s="51"/>
+      <c r="S19" s="59"/>
+    </row>
+    <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="46">
+        <f>ROW(B20) - ROW($B$9)</f>
+        <v>11</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" s="37">
+        <v>1</v>
+      </c>
+      <c r="M20" s="37">
+        <f>L20*5</f>
+        <v>5</v>
+      </c>
+      <c r="N20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="O20" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="R20" s="37"/>
+      <c r="S20" s="59"/>
+    </row>
+    <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="47">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L21" s="51">
+        <v>1</v>
+      </c>
+      <c r="M21" s="51">
+        <f t="shared" ref="M21" si="9">L21*5</f>
+        <v>5</v>
+      </c>
+      <c r="N21" s="51">
+        <v>10</v>
+      </c>
+      <c r="O21" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P21" s="52">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="Q21" s="52">
+        <f t="shared" ref="Q21" si="10">P21*N21</f>
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="R21" s="51"/>
+      <c r="S21" s="59"/>
+    </row>
+    <row r="22" spans="1:19" ht="132" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="46">
+        <f>ROW(B22) - ROW($B$9)</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f>L22*5</f>
+        <v>5</v>
+      </c>
+      <c r="N22" s="37">
+        <v>10</v>
+      </c>
+      <c r="O22" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="38">
+        <v>5.6099999999999997E-2</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.56099999999999994</v>
+      </c>
+      <c r="R22" s="37"/>
+      <c r="S22" s="59"/>
+    </row>
+    <row r="23" spans="1:19" ht="192" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="47">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51">
+        <v>1</v>
+      </c>
+      <c r="M23" s="51">
+        <f t="shared" ref="M23" si="11">L23*5</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="51">
+        <v>20</v>
+      </c>
+      <c r="O23" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P23" s="52">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" ref="Q23" si="12">P23*N23</f>
+        <v>0.67</v>
+      </c>
+      <c r="R23" s="51"/>
+      <c r="S23" s="59"/>
+    </row>
+    <row r="24" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="L24" s="37">
+        <v>5</v>
+      </c>
+      <c r="M24" s="37">
+        <f>L24*5</f>
+        <v>25</v>
+      </c>
+      <c r="N24" s="37">
+        <v>100</v>
+      </c>
+      <c r="O24" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P24" s="38">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>0.08</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="59"/>
+    </row>
+    <row r="25" spans="1:19" ht="132" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="47">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="51">
+        <v>1</v>
+      </c>
+      <c r="M25" s="51">
+        <f t="shared" ref="M25" si="13">L25*5</f>
+        <v>5</v>
+      </c>
+      <c r="N25" s="51">
+        <v>100</v>
+      </c>
+      <c r="O25" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="52">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q25" s="52">
+        <f t="shared" ref="Q25" si="14">P25*N25</f>
+        <v>0.08</v>
+      </c>
+      <c r="R25" s="51"/>
+      <c r="S25" s="59"/>
+    </row>
+    <row r="26" spans="1:19" ht="132" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="L26" s="37">
+        <v>1</v>
+      </c>
+      <c r="M26" s="37">
+        <f>L26*5</f>
+        <v>5</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P26" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="59"/>
+    </row>
+    <row r="27" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="47">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="I27" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="51">
+        <v>2</v>
+      </c>
+      <c r="M27" s="51">
+        <f t="shared" ref="M27" si="15">L27*5</f>
+        <v>10</v>
+      </c>
+      <c r="N27" s="51">
+        <v>50</v>
+      </c>
+      <c r="O27" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P27" s="52">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="52">
+        <f t="shared" ref="Q27" si="16">P27*N27</f>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="R27" s="51"/>
+      <c r="S27" s="59"/>
+    </row>
+    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="37">
+        <v>4</v>
+      </c>
+      <c r="M28" s="37">
+        <f>L28*5</f>
+        <v>20</v>
+      </c>
+      <c r="N28" s="37">
+        <v>100</v>
+      </c>
+      <c r="O28" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P28" s="38">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.09</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="59"/>
+    </row>
+    <row r="29" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="47">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="L29" s="51">
+        <v>1</v>
+      </c>
+      <c r="M29" s="51">
+        <f t="shared" ref="M29" si="17">L29*5</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="51">
+        <v>10</v>
+      </c>
+      <c r="O29" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P29" s="52">
+        <v>0.2923</v>
+      </c>
+      <c r="Q29" s="52">
+        <f t="shared" ref="Q29" si="18">P29*N29</f>
+        <v>2.923</v>
+      </c>
+      <c r="R29" s="51"/>
+      <c r="S29" s="59"/>
+    </row>
+    <row r="30" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="L30" s="37">
+        <v>1</v>
+      </c>
+      <c r="M30" s="37">
+        <f>L30*5</f>
+        <v>5</v>
+      </c>
+      <c r="N30" s="37">
+        <v>6</v>
+      </c>
+      <c r="O30" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P30" s="38">
+        <v>0.87819999999999998</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>5.2691999999999997</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="59"/>
+    </row>
+    <row r="31" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="47">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="I31" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51">
+        <v>1</v>
+      </c>
+      <c r="M31" s="51">
+        <f t="shared" ref="M31" si="19">L31*5</f>
+        <v>5</v>
+      </c>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52">
+        <f t="shared" ref="Q31" si="20">P31*N31</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="51"/>
+      <c r="S31" s="59"/>
+    </row>
+    <row r="32" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="37">
+        <f>L32*5</f>
+        <v>5</v>
+      </c>
+      <c r="N32" s="37">
+        <v>10</v>
+      </c>
+      <c r="O32" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P32" s="38">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>0.79299999999999993</v>
+      </c>
+      <c r="R32" s="37"/>
+      <c r="S32" s="59"/>
+    </row>
+    <row r="33" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="47">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J33" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51">
+        <v>1</v>
+      </c>
+      <c r="M33" s="51">
+        <f t="shared" ref="M33" si="21">L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="51">
+        <v>6</v>
+      </c>
+      <c r="O33" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P33" s="52">
+        <v>0.81779999999999997</v>
+      </c>
+      <c r="Q33" s="52">
+        <f t="shared" ref="Q33" si="22">P33*N33</f>
+        <v>4.9067999999999996</v>
+      </c>
+      <c r="R33" s="51"/>
+      <c r="S33" s="59"/>
+    </row>
+    <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f>L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="37">
+        <v>10</v>
+      </c>
+      <c r="O34" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.1444</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>1.444</v>
+      </c>
+      <c r="R34" s="37"/>
+      <c r="S34" s="59"/>
+    </row>
+    <row r="35" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="47">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51">
+        <v>1</v>
+      </c>
+      <c r="M35" s="51">
+        <f t="shared" ref="M35" si="23">L35*5</f>
+        <v>5</v>
+      </c>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52">
+        <f t="shared" ref="Q35" si="24">P35*N35</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="51"/>
+      <c r="S35" s="59"/>
+    </row>
+    <row r="36" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="46">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f>L36*5</f>
+        <v>5</v>
+      </c>
+      <c r="N36" s="37">
+        <v>6</v>
+      </c>
+      <c r="O36" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P36" s="38">
+        <v>0.33260000000000001</v>
+      </c>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
+        <v>1.9956</v>
+      </c>
+      <c r="R36" s="37"/>
+      <c r="S36" s="59"/>
+    </row>
+    <row r="37" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="47">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="K37" s="51"/>
+      <c r="L37" s="51">
+        <v>1</v>
+      </c>
+      <c r="M37" s="51">
+        <f t="shared" ref="M37" si="25">L37*5</f>
+        <v>5</v>
+      </c>
+      <c r="N37" s="51">
+        <v>6</v>
+      </c>
+      <c r="O37" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="P37" s="52">
+        <v>2.3832</v>
+      </c>
+      <c r="Q37" s="52">
+        <f t="shared" ref="Q37" si="26">P37*N37</f>
+        <v>14.299199999999999</v>
+      </c>
+      <c r="R37" s="51"/>
+      <c r="S37" s="59"/>
+    </row>
+    <row r="38" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="46">
+        <f>ROW(B38) - ROW($B$9)</f>
+        <v>29</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37">
+        <v>1</v>
+      </c>
+      <c r="M38" s="37">
+        <f>L38*5</f>
+        <v>5</v>
+      </c>
+      <c r="N38" s="37">
+        <v>6</v>
+      </c>
+      <c r="O38" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="P38" s="38">
+        <v>1.6069</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>9.6414000000000009</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="O39" s="69"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="48">
+        <f>SUM(Q10:Q38)</f>
+        <v>50.671000000000006</v>
+      </c>
+      <c r="R39" s="64"/>
+      <c r="S39" s="65"/>
+    </row>
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="O40" s="69"/>
+      <c r="P40" s="69"/>
+      <c r="Q40" s="49">
+        <f>Q39/5</f>
+        <v>10.134200000000002</v>
+      </c>
+      <c r="R40" s="66"/>
+      <c r="S40" s="67"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S40"/>
+    <mergeCell ref="N40:P40"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O15" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O21" r:id="rId7"/>
+    <hyperlink ref="O22" r:id="rId8"/>
+    <hyperlink ref="O23" r:id="rId9"/>
+    <hyperlink ref="O24" r:id="rId10"/>
+    <hyperlink ref="O25" r:id="rId11"/>
+    <hyperlink ref="O26" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O28" r:id="rId14"/>
+    <hyperlink ref="O29" r:id="rId15"/>
+    <hyperlink ref="O30" r:id="rId16"/>
+    <hyperlink ref="O32" r:id="rId17"/>
+    <hyperlink ref="O33" r:id="rId18"/>
+    <hyperlink ref="O34" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O12" r:id="rId23"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>
--- a/Design Files/BLE_product-v1.0/BOM/eSpark_BOM_BLE_product-v1.0.xlsx
+++ b/Design Files/BLE_product-v1.0/BOM/eSpark_BOM_BLE_product-v1.0.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="215">
   <si>
     <t>Component list</t>
   </si>
@@ -558,21 +558,9 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Quantity (5 Boards)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOQ (5 Boards)</t>
-  </si>
-  <si>
     <t>Links</t>
   </si>
   <si>
-    <t>Unit Cost (5 Boards)</t>
-  </si>
-  <si>
-    <t>Total Cost (5 Boards)</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -643,6 +631,43 @@
   </si>
   <si>
     <t>Total Cost (50 Boards)</t>
+  </si>
+  <si>
+    <t>Peripherals</t>
+  </si>
+  <si>
+    <t>dc2.0*0.5mm USB Charger Cable Small Pin Charging Cord</t>
+  </si>
+  <si>
+    <t>USB DC 2.0*0.5mm Charging Cable for Mini S530 Smallest Invisible Wireless Bluetooth Earbuds Earphones Headphones Headset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“No Legs” 6-pin Plug-of-Nails™ Cable fitted with a 6-pin 0.1″ pitch ribbon connector.
+</t>
+  </si>
+  <si>
+    <t>TC2030-IDC-NL</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Tag Connect</t>
+  </si>
+  <si>
+    <t>Chipsmall</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -654,7 +679,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,6 +856,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -858,7 +890,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1129,12 +1161,116 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1295,6 +1431,36 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1327,34 +1493,114 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1553,14 +1799,14 @@
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -1584,7 +1830,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19545300" y="620017"/>
+          <a:off x="18430875" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1861,7 +2107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1877,7 +2123,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -1895,15 +2141,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1914,7 +2160,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1939,7 +2185,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1953,7 +2199,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1964,7 +2210,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1978,7 +2224,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2003,7 +2249,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2024,7 +2270,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2045,7 +2291,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2066,7 +2312,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2104,25 +2350,25 @@
         <v>175</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="O9" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>180</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2150,7 +2396,7 @@
         <v>125</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>141</v>
@@ -2168,8 +2414,8 @@
       <c r="N10" s="37">
         <v>100</v>
       </c>
-      <c r="O10" s="70" t="s">
-        <v>191</v>
+      <c r="O10" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P10" s="38">
         <v>1.1000000000000001E-3</v>
@@ -2206,7 +2452,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J11" s="51" t="s">
         <v>142</v>
@@ -2218,14 +2464,14 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M38" si="1">L11*10</f>
+        <f t="shared" ref="M11:M41" si="1">L11*10</f>
         <v>10</v>
       </c>
       <c r="N11" s="51">
         <v>50</v>
       </c>
-      <c r="O11" s="71" t="s">
-        <v>191</v>
+      <c r="O11" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P11" s="52">
         <v>1.09E-2</v>
@@ -2255,17 +2501,17 @@
       <c r="F12" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="76" t="s">
+      <c r="G12" s="66" t="s">
         <v>104</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>125</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K12" s="37" t="s">
         <v>165</v>
@@ -2280,8 +2526,8 @@
       <c r="N12" s="37">
         <v>50</v>
       </c>
-      <c r="O12" s="70" t="s">
-        <v>191</v>
+      <c r="O12" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P12" s="38">
         <v>1.35E-2</v>
@@ -2318,7 +2564,7 @@
         <v>125</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J13" s="51" t="s">
         <v>143</v>
@@ -2336,8 +2582,8 @@
       <c r="N13" s="51">
         <v>100</v>
       </c>
-      <c r="O13" s="71" t="s">
-        <v>191</v>
+      <c r="O13" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P13" s="52">
         <v>5.3E-3</v>
@@ -2374,7 +2620,7 @@
         <v>125</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>144</v>
@@ -2392,8 +2638,8 @@
       <c r="N14" s="37">
         <v>20</v>
       </c>
-      <c r="O14" s="70" t="s">
-        <v>191</v>
+      <c r="O14" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P14" s="38">
         <v>3.44E-2</v>
@@ -2421,7 +2667,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>82</v>
@@ -2430,7 +2676,7 @@
         <v>127</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J15" s="51" t="s">
         <v>145</v>
@@ -2448,8 +2694,8 @@
       <c r="N15" s="51">
         <v>11</v>
       </c>
-      <c r="O15" s="71" t="s">
-        <v>191</v>
+      <c r="O15" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P15" s="52">
         <v>0.50600000000000001</v>
@@ -2486,7 +2732,7 @@
         <v>125</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>146</v>
@@ -2504,8 +2750,8 @@
       <c r="N16" s="37">
         <v>20</v>
       </c>
-      <c r="O16" s="70" t="s">
-        <v>191</v>
+      <c r="O16" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P16" s="38">
         <v>6.3100000000000003E-2</v>
@@ -2523,55 +2769,55 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="G17" s="73" t="s">
+      <c r="F17" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73">
+      <c r="H17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63">
         <v>4</v>
       </c>
       <c r="M17" s="37">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="R17" s="73"/>
-      <c r="S17" s="75"/>
-    </row>
-    <row r="18" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="N17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P17" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q17" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" s="63"/>
+      <c r="S17" s="65"/>
+    </row>
+    <row r="18" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="95"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -2594,9 +2840,15 @@
       <c r="H18" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
+      <c r="I18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L18" s="37">
         <v>1</v>
       </c>
@@ -2604,12 +2856,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="38"/>
+      <c r="N18" s="37">
+        <v>12</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="38">
+        <v>0.68</v>
+      </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>0</v>
+        <v>8.16</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -2620,51 +2878,51 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="G19" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="L19" s="73">
+      <c r="H19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" s="63">
         <v>1</v>
       </c>
       <c r="M19" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P19" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q19" s="74" t="s">
-        <v>189</v>
+      <c r="N19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P19" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q19" s="64" t="s">
+        <v>185</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -2675,52 +2933,54 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="76" t="s">
+      <c r="C20" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="76" t="s">
+      <c r="E20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="J20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="K20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="L20" s="76">
-        <v>1</v>
-      </c>
-      <c r="M20" s="76">
+      <c r="G20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="66">
+        <v>1</v>
+      </c>
+      <c r="M20" s="66">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="O20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78" t="s">
-        <v>189</v>
-      </c>
-      <c r="R20" s="76"/>
-      <c r="S20" s="75"/>
+      <c r="N20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="O20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q20" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="R20" s="66"/>
+      <c r="S20" s="65"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -2747,7 +3007,7 @@
         <v>129</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J21" s="51" t="s">
         <v>147</v>
@@ -2765,8 +3025,8 @@
       <c r="N21" s="51">
         <v>15</v>
       </c>
-      <c r="O21" s="71" t="s">
-        <v>191</v>
+      <c r="O21" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P21" s="52">
         <v>8.4000000000000005E-2</v>
@@ -2794,7 +3054,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>88</v>
@@ -2803,13 +3063,13 @@
         <v>130</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J22" s="37" t="s">
         <v>148</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2821,8 +3081,8 @@
       <c r="N22" s="37">
         <v>20</v>
       </c>
-      <c r="O22" s="70" t="s">
-        <v>191</v>
+      <c r="O22" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P22" s="38">
         <v>5.6099999999999997E-2</v>
@@ -2859,12 +3119,14 @@
         <v>131</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J23" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="51"/>
+      <c r="K23" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L23" s="51">
         <v>1</v>
       </c>
@@ -2875,8 +3137,8 @@
       <c r="N23" s="51">
         <v>20</v>
       </c>
-      <c r="O23" s="71" t="s">
-        <v>191</v>
+      <c r="O23" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P23" s="52">
         <v>3.3500000000000002E-2</v>
@@ -2913,7 +3175,7 @@
         <v>125</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J24" s="37" t="s">
         <v>150</v>
@@ -2931,8 +3193,8 @@
       <c r="N24" s="37">
         <v>100</v>
       </c>
-      <c r="O24" s="70" t="s">
-        <v>191</v>
+      <c r="O24" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P24" s="38">
         <v>8.0000000000000004E-4</v>
@@ -2969,7 +3231,7 @@
         <v>132</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J25" s="51" t="s">
         <v>151</v>
@@ -2987,8 +3249,8 @@
       <c r="N25" s="51">
         <v>100</v>
       </c>
-      <c r="O25" s="71" t="s">
-        <v>191</v>
+      <c r="O25" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P25" s="52">
         <v>8.0000000000000004E-4</v>
@@ -3025,7 +3287,7 @@
         <v>132</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J26" s="37" t="s">
         <v>152</v>
@@ -3043,8 +3305,8 @@
       <c r="N26" s="37">
         <v>100</v>
       </c>
-      <c r="O26" s="70" t="s">
-        <v>191</v>
+      <c r="O26" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P26" s="38">
         <v>6.9999999999999999E-4</v>
@@ -3081,7 +3343,7 @@
         <v>132</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J27" s="51" t="s">
         <v>153</v>
@@ -3099,8 +3361,8 @@
       <c r="N27" s="51">
         <v>50</v>
       </c>
-      <c r="O27" s="71" t="s">
-        <v>191</v>
+      <c r="O27" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P27" s="52">
         <v>4.5999999999999999E-3</v>
@@ -3137,7 +3399,7 @@
         <v>125</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J28" s="37" t="s">
         <v>154</v>
@@ -3155,8 +3417,8 @@
       <c r="N28" s="37">
         <v>100</v>
       </c>
-      <c r="O28" s="70" t="s">
-        <v>191</v>
+      <c r="O28" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P28" s="38">
         <v>8.9999999999999998E-4</v>
@@ -3193,13 +3455,13 @@
         <v>133</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J29" s="51" t="s">
         <v>155</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3211,8 +3473,8 @@
       <c r="N29" s="51">
         <v>15</v>
       </c>
-      <c r="O29" s="71" t="s">
-        <v>191</v>
+      <c r="O29" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P29" s="52">
         <v>0.2923</v>
@@ -3249,13 +3511,13 @@
         <v>134</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J30" s="37" t="s">
         <v>156</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3267,8 +3529,8 @@
       <c r="N30" s="37">
         <v>11</v>
       </c>
-      <c r="O30" s="70" t="s">
-        <v>191</v>
+      <c r="O30" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P30" s="38">
         <v>0.87819999999999998</v>
@@ -3305,12 +3567,14 @@
         <v>135</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J31" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="K31" s="51"/>
+      <c r="K31" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L31" s="51">
         <v>1</v>
       </c>
@@ -3318,12 +3582,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="52"/>
+      <c r="N31" s="51">
+        <v>11</v>
+      </c>
+      <c r="O31" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="P31" s="52">
+        <v>2.7</v>
+      </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="10">P31*N31</f>
-        <v>0</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
@@ -3353,12 +3623,14 @@
         <v>136</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J32" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K32" s="37"/>
+      <c r="K32" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L32" s="37">
         <v>1</v>
       </c>
@@ -3369,8 +3641,8 @@
       <c r="N32" s="37">
         <v>15</v>
       </c>
-      <c r="O32" s="70" t="s">
-        <v>191</v>
+      <c r="O32" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P32" s="38">
         <v>7.9299999999999995E-2</v>
@@ -3401,18 +3673,20 @@
         <v>95</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H33" s="51" t="s">
         <v>137</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="K33" s="51"/>
+        <v>182</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L33" s="51">
         <v>1</v>
       </c>
@@ -3423,8 +3697,8 @@
       <c r="N33" s="51">
         <v>11</v>
       </c>
-      <c r="O33" s="71" t="s">
-        <v>191</v>
+      <c r="O33" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P33" s="52">
         <v>0.6794</v>
@@ -3461,12 +3735,14 @@
         <v>136</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J34" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K34" s="37"/>
+      <c r="K34" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L34" s="37">
         <v>1</v>
       </c>
@@ -3477,8 +3753,8 @@
       <c r="N34" s="37">
         <v>15</v>
       </c>
-      <c r="O34" s="70" t="s">
-        <v>191</v>
+      <c r="O34" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P34" s="38">
         <v>0.1444</v>
@@ -3515,10 +3791,14 @@
         <v>138</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
+        <v>185</v>
+      </c>
+      <c r="J35" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="K35" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L35" s="51">
         <v>1</v>
       </c>
@@ -3526,12 +3806,18 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="52"/>
+      <c r="N35" s="51">
+        <v>11</v>
+      </c>
+      <c r="O35" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="P35" s="52">
+        <v>18.221</v>
+      </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="12">P35*N35</f>
-        <v>0</v>
+        <v>200.43100000000001</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
@@ -3561,12 +3847,14 @@
         <v>137</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J36" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="K36" s="37"/>
+      <c r="K36" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L36" s="37">
         <v>1</v>
       </c>
@@ -3577,8 +3865,8 @@
       <c r="N36" s="37">
         <v>11</v>
       </c>
-      <c r="O36" s="70" t="s">
-        <v>191</v>
+      <c r="O36" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P36" s="38">
         <v>0.33260000000000001</v>
@@ -3618,7 +3906,9 @@
       <c r="J37" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="K37" s="51"/>
+      <c r="K37" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
@@ -3629,8 +3919,8 @@
       <c r="N37" s="51">
         <v>11</v>
       </c>
-      <c r="O37" s="71" t="s">
-        <v>191</v>
+      <c r="O37" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P37" s="52">
         <v>2.1604999999999999</v>
@@ -3670,7 +3960,9 @@
       <c r="J38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="37"/>
+      <c r="K38" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -3681,8 +3973,8 @@
       <c r="N38" s="37">
         <v>11</v>
       </c>
-      <c r="O38" s="70" t="s">
-        <v>191</v>
+      <c r="O38" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P38" s="38">
         <v>1.3826000000000001</v>
@@ -3694,65 +3986,233 @@
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="68" t="s">
+      <c r="B39" s="46">
+        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="83">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N39" s="91">
+        <v>11</v>
+      </c>
+      <c r="O39" s="97" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" s="93">
+        <v>3.46</v>
+      </c>
+      <c r="Q39" s="38">
+        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
+        <v>38.06</v>
+      </c>
+      <c r="R39" s="91"/>
+      <c r="S39" s="91"/>
+    </row>
+    <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="46">
+        <f t="shared" si="14"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J40" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="L40" s="83">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N40" s="51">
+        <v>11</v>
+      </c>
+      <c r="O40" s="98" t="s">
+        <v>208</v>
+      </c>
+      <c r="P40" s="52">
+        <v>3.15</v>
+      </c>
+      <c r="Q40" s="38">
+        <f t="shared" si="15"/>
+        <v>34.65</v>
+      </c>
+      <c r="R40" s="51"/>
+      <c r="S40" s="51"/>
+    </row>
+    <row r="41" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="46">
+        <f t="shared" si="14"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E41" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G41" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J41" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K41" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L41" s="83">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N41" s="39">
+        <v>1</v>
+      </c>
+      <c r="O41" s="99" t="s">
+        <v>209</v>
+      </c>
+      <c r="P41" s="94">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="Q41" s="38">
+        <f t="shared" si="15"/>
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R41" s="39"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="48">
+      <c r="O42" s="79"/>
+      <c r="P42" s="79"/>
+      <c r="Q42" s="48">
         <f>SUM(Q10:Q38)</f>
-        <v>80.484300000000005</v>
-      </c>
-      <c r="R39" s="64"/>
-      <c r="S39" s="65"/>
-    </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="68" t="s">
+        <v>318.77529999999996</v>
+      </c>
+      <c r="R42" s="74"/>
+      <c r="S42" s="75"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O40" s="69"/>
-      <c r="P40" s="69"/>
-      <c r="Q40" s="49">
-        <f>Q39/10</f>
-        <v>8.0484299999999998</v>
-      </c>
-      <c r="R40" s="66"/>
-      <c r="S40" s="67"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="49">
+        <f>Q42/10</f>
+        <v>31.877529999999997</v>
+      </c>
+      <c r="R43" s="76"/>
+      <c r="S43" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R39:S40"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -3778,16 +4238,21 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
+    <hyperlink ref="O18" r:id="rId24" location="nav-specification"/>
+    <hyperlink ref="O35" r:id="rId25"/>
+    <hyperlink ref="O41" r:id="rId26"/>
+    <hyperlink ref="O40" r:id="rId27"/>
+    <hyperlink ref="O39" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
-  <drawing r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
+  <drawing r:id="rId30"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -3803,7 +4268,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -3821,15 +4286,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3840,7 +4305,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -3865,7 +4330,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -3879,7 +4344,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3890,7 +4355,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -3904,7 +4369,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3929,7 +4394,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3950,7 +4415,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3971,7 +4436,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3992,7 +4457,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4030,25 +4495,25 @@
         <v>175</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="O9" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>180</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -4076,7 +4541,7 @@
         <v>125</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>141</v>
@@ -4094,8 +4559,8 @@
       <c r="N10" s="37">
         <v>200</v>
       </c>
-      <c r="O10" s="70" t="s">
-        <v>191</v>
+      <c r="O10" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P10" s="38">
         <v>1.1000000000000001E-3</v>
@@ -4132,7 +4597,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J11" s="51" t="s">
         <v>142</v>
@@ -4144,14 +4609,14 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M38" si="1">L11*20</f>
+        <f t="shared" ref="M11:M41" si="1">L11*20</f>
         <v>20</v>
       </c>
       <c r="N11" s="51">
         <v>50</v>
       </c>
-      <c r="O11" s="71" t="s">
-        <v>191</v>
+      <c r="O11" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P11" s="52">
         <v>1.09E-2</v>
@@ -4181,17 +4646,17 @@
       <c r="F12" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="76" t="s">
+      <c r="G12" s="66" t="s">
         <v>104</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>125</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K12" s="37" t="s">
         <v>165</v>
@@ -4206,8 +4671,8 @@
       <c r="N12" s="37">
         <v>50</v>
       </c>
-      <c r="O12" s="70" t="s">
-        <v>191</v>
+      <c r="O12" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P12" s="38">
         <v>1.35E-2</v>
@@ -4244,7 +4709,7 @@
         <v>125</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J13" s="51" t="s">
         <v>143</v>
@@ -4262,8 +4727,8 @@
       <c r="N13" s="51">
         <v>100</v>
       </c>
-      <c r="O13" s="71" t="s">
-        <v>191</v>
+      <c r="O13" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P13" s="52">
         <v>5.3E-3</v>
@@ -4300,7 +4765,7 @@
         <v>125</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>144</v>
@@ -4318,8 +4783,8 @@
       <c r="N14" s="37">
         <v>40</v>
       </c>
-      <c r="O14" s="70" t="s">
-        <v>191</v>
+      <c r="O14" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P14" s="38">
         <v>3.44E-2</v>
@@ -4347,7 +4812,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>82</v>
@@ -4356,7 +4821,7 @@
         <v>127</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J15" s="51" t="s">
         <v>145</v>
@@ -4374,8 +4839,8 @@
       <c r="N15" s="51">
         <v>21</v>
       </c>
-      <c r="O15" s="71" t="s">
-        <v>191</v>
+      <c r="O15" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P15" s="52">
         <v>0.50600000000000001</v>
@@ -4412,7 +4877,7 @@
         <v>125</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>146</v>
@@ -4430,8 +4895,8 @@
       <c r="N16" s="37">
         <v>30</v>
       </c>
-      <c r="O16" s="70" t="s">
-        <v>191</v>
+      <c r="O16" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P16" s="38">
         <v>6.3100000000000003E-2</v>
@@ -4449,52 +4914,52 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="G17" s="73" t="s">
+      <c r="F17" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73">
+      <c r="H17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63">
         <v>4</v>
       </c>
       <c r="M17" s="37">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="R17" s="73"/>
-      <c r="S17" s="75"/>
+      <c r="N17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P17" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q17" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" s="63"/>
+      <c r="S17" s="65"/>
     </row>
     <row r="18" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -4520,9 +4985,15 @@
       <c r="H18" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
+      <c r="I18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L18" s="37">
         <v>1</v>
       </c>
@@ -4530,12 +5001,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="38"/>
+      <c r="N18" s="37">
+        <v>21</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="38">
+        <v>0.68</v>
+      </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>0</v>
+        <v>14.280000000000001</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -4546,51 +5023,51 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="G19" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="L19" s="73">
-        <v>1</v>
-      </c>
-      <c r="M19" s="73">
+      <c r="H19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" s="63">
+        <v>1</v>
+      </c>
+      <c r="M19" s="63">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P19" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q19" s="74" t="s">
-        <v>189</v>
+      <c r="N19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P19" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q19" s="64" t="s">
+        <v>185</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -4601,52 +5078,52 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="76" t="s">
+      <c r="C20" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="79" t="s">
-        <v>189</v>
-      </c>
-      <c r="G20" s="76" t="s">
+      <c r="E20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="69" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="J20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="K20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="L20" s="76">
-        <v>1</v>
-      </c>
-      <c r="M20" s="76">
+      <c r="H20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="66">
+        <v>1</v>
+      </c>
+      <c r="M20" s="66">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="O20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78" t="s">
-        <v>189</v>
-      </c>
-      <c r="R20" s="76"/>
-      <c r="S20" s="75"/>
+      <c r="N20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="O20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="R20" s="66"/>
+      <c r="S20" s="65"/>
     </row>
     <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -4673,7 +5150,7 @@
         <v>129</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J21" s="51" t="s">
         <v>147</v>
@@ -4691,8 +5168,8 @@
       <c r="N21" s="51">
         <v>25</v>
       </c>
-      <c r="O21" s="71" t="s">
-        <v>191</v>
+      <c r="O21" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P21" s="52">
         <v>8.4000000000000005E-2</v>
@@ -4720,7 +5197,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>88</v>
@@ -4729,13 +5206,13 @@
         <v>130</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J22" s="37" t="s">
         <v>148</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -4747,8 +5224,8 @@
       <c r="N22" s="37">
         <v>30</v>
       </c>
-      <c r="O22" s="70" t="s">
-        <v>191</v>
+      <c r="O22" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P22" s="38">
         <v>5.6099999999999997E-2</v>
@@ -4785,7 +5262,7 @@
         <v>131</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J23" s="51" t="s">
         <v>149</v>
@@ -4801,8 +5278,8 @@
       <c r="N23" s="51">
         <v>40</v>
       </c>
-      <c r="O23" s="71" t="s">
-        <v>191</v>
+      <c r="O23" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P23" s="52">
         <v>3.3500000000000002E-2</v>
@@ -4839,7 +5316,7 @@
         <v>125</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J24" s="37" t="s">
         <v>150</v>
@@ -4857,8 +5334,8 @@
       <c r="N24" s="37">
         <v>200</v>
       </c>
-      <c r="O24" s="70" t="s">
-        <v>191</v>
+      <c r="O24" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P24" s="38">
         <v>8.0000000000000004E-4</v>
@@ -4895,7 +5372,7 @@
         <v>132</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J25" s="51" t="s">
         <v>151</v>
@@ -4913,8 +5390,8 @@
       <c r="N25" s="51">
         <v>100</v>
       </c>
-      <c r="O25" s="71" t="s">
-        <v>191</v>
+      <c r="O25" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P25" s="52">
         <v>8.0000000000000004E-4</v>
@@ -4951,7 +5428,7 @@
         <v>132</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J26" s="37" t="s">
         <v>152</v>
@@ -4969,8 +5446,8 @@
       <c r="N26" s="37">
         <v>100</v>
       </c>
-      <c r="O26" s="70" t="s">
-        <v>191</v>
+      <c r="O26" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P26" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5007,7 +5484,7 @@
         <v>132</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J27" s="51" t="s">
         <v>153</v>
@@ -5025,8 +5502,8 @@
       <c r="N27" s="51">
         <v>50</v>
       </c>
-      <c r="O27" s="71" t="s">
-        <v>191</v>
+      <c r="O27" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P27" s="52">
         <v>4.5999999999999999E-3</v>
@@ -5063,7 +5540,7 @@
         <v>125</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J28" s="37" t="s">
         <v>154</v>
@@ -5081,8 +5558,8 @@
       <c r="N28" s="37">
         <v>100</v>
       </c>
-      <c r="O28" s="70" t="s">
-        <v>191</v>
+      <c r="O28" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P28" s="38">
         <v>8.9999999999999998E-4</v>
@@ -5119,13 +5596,13 @@
         <v>133</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J29" s="51" t="s">
         <v>155</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -5137,8 +5614,8 @@
       <c r="N29" s="51">
         <v>25</v>
       </c>
-      <c r="O29" s="71" t="s">
-        <v>191</v>
+      <c r="O29" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P29" s="52">
         <v>0.2923</v>
@@ -5175,13 +5652,13 @@
         <v>134</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J30" s="37" t="s">
         <v>156</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -5193,8 +5670,8 @@
       <c r="N30" s="37">
         <v>21</v>
       </c>
-      <c r="O30" s="70" t="s">
-        <v>191</v>
+      <c r="O30" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P30" s="38">
         <v>0.73980000000000001</v>
@@ -5231,12 +5708,14 @@
         <v>135</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="K31" s="51"/>
+        <v>185</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L31" s="51">
         <v>1</v>
       </c>
@@ -5244,12 +5723,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="52"/>
+      <c r="N31" s="51">
+        <v>21</v>
+      </c>
+      <c r="O31" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="P31" s="52">
+        <v>2.7</v>
+      </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="10">P31*N31</f>
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
@@ -5279,12 +5764,14 @@
         <v>136</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J32" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K32" s="37"/>
+      <c r="K32" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L32" s="37">
         <v>1</v>
       </c>
@@ -5295,8 +5782,8 @@
       <c r="N32" s="37">
         <v>25</v>
       </c>
-      <c r="O32" s="70" t="s">
-        <v>191</v>
+      <c r="O32" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P32" s="38">
         <v>7.9299999999999995E-2</v>
@@ -5327,18 +5814,20 @@
         <v>95</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H33" s="51" t="s">
         <v>137</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="K33" s="51"/>
+        <v>182</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L33" s="51">
         <v>1</v>
       </c>
@@ -5349,8 +5838,8 @@
       <c r="N33" s="51">
         <v>21</v>
       </c>
-      <c r="O33" s="71" t="s">
-        <v>191</v>
+      <c r="O33" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P33" s="52">
         <v>0.6794</v>
@@ -5387,12 +5876,14 @@
         <v>136</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J34" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K34" s="37"/>
+      <c r="K34" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L34" s="37">
         <v>1</v>
       </c>
@@ -5403,8 +5894,8 @@
       <c r="N34" s="37">
         <v>25</v>
       </c>
-      <c r="O34" s="70" t="s">
-        <v>191</v>
+      <c r="O34" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P34" s="38">
         <v>0.1444</v>
@@ -5441,10 +5932,14 @@
         <v>138</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
+        <v>185</v>
+      </c>
+      <c r="J35" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="K35" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L35" s="51">
         <v>1</v>
       </c>
@@ -5452,12 +5947,18 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="52"/>
+      <c r="N35" s="51">
+        <v>21</v>
+      </c>
+      <c r="O35" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="P35" s="52">
+        <v>18.221</v>
+      </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="12">P35*N35</f>
-        <v>0</v>
+        <v>382.64100000000002</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
@@ -5487,12 +5988,14 @@
         <v>137</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J36" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="K36" s="37"/>
+      <c r="K36" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L36" s="37">
         <v>1</v>
       </c>
@@ -5503,8 +6006,8 @@
       <c r="N36" s="37">
         <v>21</v>
       </c>
-      <c r="O36" s="70" t="s">
-        <v>191</v>
+      <c r="O36" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P36" s="38">
         <v>0.33260000000000001</v>
@@ -5540,11 +6043,15 @@
       <c r="H37" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="I37" s="51"/>
+      <c r="I37" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="J37" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="K37" s="51"/>
+      <c r="K37" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
@@ -5555,8 +6062,8 @@
       <c r="N37" s="51">
         <v>21</v>
       </c>
-      <c r="O37" s="71" t="s">
-        <v>191</v>
+      <c r="O37" s="61" t="s">
+        <v>187</v>
       </c>
       <c r="P37" s="52">
         <v>2.1604999999999999</v>
@@ -5592,11 +6099,15 @@
       <c r="H38" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="37"/>
+      <c r="I38" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="J38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="37"/>
+      <c r="K38" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -5607,8 +6118,8 @@
       <c r="N38" s="37">
         <v>21</v>
       </c>
-      <c r="O38" s="70" t="s">
-        <v>191</v>
+      <c r="O38" s="60" t="s">
+        <v>187</v>
       </c>
       <c r="P38" s="38">
         <v>1.3826000000000001</v>
@@ -5620,65 +6131,231 @@
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="68" t="s">
+      <c r="B39" s="46">
+        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="83">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N39" s="91">
+        <v>21</v>
+      </c>
+      <c r="O39" s="97" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" s="93">
+        <v>3.46</v>
+      </c>
+      <c r="Q39" s="38">
+        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
+        <v>72.66</v>
+      </c>
+      <c r="R39" s="91"/>
+      <c r="S39" s="91"/>
+    </row>
+    <row r="40" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="46">
+        <f t="shared" si="14"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J40" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="L40" s="83">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N40" s="51">
+        <v>21</v>
+      </c>
+      <c r="O40" s="98" t="s">
+        <v>208</v>
+      </c>
+      <c r="P40" s="52">
+        <v>3.15</v>
+      </c>
+      <c r="Q40" s="38">
+        <f t="shared" si="15"/>
+        <v>66.149999999999991</v>
+      </c>
+      <c r="R40" s="51"/>
+      <c r="S40" s="51"/>
+    </row>
+    <row r="41" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="46">
+        <f t="shared" si="14"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="37"/>
+      <c r="E41" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G41" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J41" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K41" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L41" s="83">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N41" s="39">
+        <v>1</v>
+      </c>
+      <c r="O41" s="99" t="s">
+        <v>209</v>
+      </c>
+      <c r="P41" s="94">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="Q41" s="38">
+        <f t="shared" si="15"/>
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R41" s="39"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="48">
+      <c r="O42" s="79"/>
+      <c r="P42" s="79"/>
+      <c r="Q42" s="48">
         <f>SUM(Q10:Q38)</f>
-        <v>145.71090000000001</v>
-      </c>
-      <c r="R39" s="64"/>
-      <c r="S39" s="65"/>
-    </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="68" t="s">
+        <v>599.33190000000002</v>
+      </c>
+      <c r="R42" s="74"/>
+      <c r="S42" s="75"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O40" s="69"/>
-      <c r="P40" s="69"/>
-      <c r="Q40" s="49">
-        <f>Q39/20</f>
-        <v>7.2855450000000008</v>
-      </c>
-      <c r="R40" s="66"/>
-      <c r="S40" s="67"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="49">
+        <f>Q42/20</f>
+        <v>29.966595000000002</v>
+      </c>
+      <c r="R43" s="76"/>
+      <c r="S43" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S40"/>
-    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -5704,15 +6381,20 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
+    <hyperlink ref="O41" r:id="rId24"/>
+    <hyperlink ref="O40" r:id="rId25"/>
+    <hyperlink ref="O39" r:id="rId26"/>
+    <hyperlink ref="O35" r:id="rId27"/>
+    <hyperlink ref="O18" r:id="rId28" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -5728,7 +6410,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -5746,15 +6428,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5765,7 +6447,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -5790,7 +6472,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -5804,7 +6486,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5815,7 +6497,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -5829,7 +6511,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5854,7 +6536,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5875,7 +6557,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5896,7 +6578,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5917,7 +6599,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5955,25 +6637,25 @@
         <v>175</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O9" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="R9" s="111" t="s">
+        <v>179</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>180</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -6001,7 +6683,7 @@
         <v>125</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>141</v>
@@ -6019,17 +6701,17 @@
       <c r="N10" s="37">
         <v>400</v>
       </c>
-      <c r="O10" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P10" s="38">
+      <c r="O10" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P10" s="108">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
         <v>0.44</v>
       </c>
-      <c r="R10" s="37"/>
+      <c r="R10" s="83"/>
       <c r="S10" s="50"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -6057,7 +6739,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J11" s="51" t="s">
         <v>142</v>
@@ -6069,23 +6751,23 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M38" si="1">L11*50</f>
+        <f t="shared" ref="M11:M41" si="1">L11*50</f>
         <v>50</v>
       </c>
       <c r="N11" s="51">
         <v>100</v>
       </c>
-      <c r="O11" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P11" s="52">
+      <c r="O11" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P11" s="102">
         <v>1.09E-2</v>
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>1.0900000000000001</v>
       </c>
-      <c r="R11" s="51"/>
+      <c r="R11" s="105"/>
       <c r="S11" s="51"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -6106,17 +6788,17 @@
       <c r="F12" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="76" t="s">
+      <c r="G12" s="66" t="s">
         <v>104</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>125</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K12" s="37" t="s">
         <v>165</v>
@@ -6131,17 +6813,17 @@
       <c r="N12" s="37">
         <v>100</v>
       </c>
-      <c r="O12" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P12" s="38">
+      <c r="O12" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P12" s="108">
         <v>1.35E-2</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
         <v>1.35</v>
       </c>
-      <c r="R12" s="37"/>
+      <c r="R12" s="83"/>
       <c r="S12" s="59"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -6169,7 +6851,7 @@
         <v>125</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J13" s="51" t="s">
         <v>143</v>
@@ -6187,17 +6869,17 @@
       <c r="N13" s="51">
         <v>100</v>
       </c>
-      <c r="O13" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P13" s="52">
+      <c r="O13" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P13" s="102">
         <v>5.3E-3</v>
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
         <v>0.53</v>
       </c>
-      <c r="R13" s="51"/>
+      <c r="R13" s="105"/>
       <c r="S13" s="59"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -6225,7 +6907,7 @@
         <v>125</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>144</v>
@@ -6243,17 +6925,17 @@
       <c r="N14" s="37">
         <v>60</v>
       </c>
-      <c r="O14" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P14" s="38">
+      <c r="O14" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P14" s="108">
         <v>3.44E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
         <v>2.0640000000000001</v>
       </c>
-      <c r="R14" s="37"/>
+      <c r="R14" s="83"/>
       <c r="S14" s="59"/>
     </row>
     <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -6272,7 +6954,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>82</v>
@@ -6281,7 +6963,7 @@
         <v>127</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J15" s="51" t="s">
         <v>145</v>
@@ -6299,17 +6981,17 @@
       <c r="N15" s="51">
         <v>51</v>
       </c>
-      <c r="O15" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P15" s="52">
+      <c r="O15" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P15" s="102">
         <v>0.45979999999999999</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
         <v>23.4498</v>
       </c>
-      <c r="R15" s="51"/>
+      <c r="R15" s="105"/>
       <c r="S15" s="59"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -6337,7 +7019,7 @@
         <v>125</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>146</v>
@@ -6355,17 +7037,17 @@
       <c r="N16" s="37">
         <v>60</v>
       </c>
-      <c r="O16" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P16" s="38">
+      <c r="O16" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P16" s="108">
         <v>6.3100000000000003E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
         <v>3.786</v>
       </c>
-      <c r="R16" s="37"/>
+      <c r="R16" s="83"/>
       <c r="S16" s="59"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -6374,54 +7056,54 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="G17" s="73" t="s">
+      <c r="F17" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="L17" s="73">
+      <c r="H17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="L17" s="63">
         <v>4</v>
       </c>
-      <c r="M17" s="73">
+      <c r="M17" s="63">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="N17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="R17" s="73"/>
-      <c r="S17" s="75"/>
+      <c r="N17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P17" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q17" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" s="112"/>
+      <c r="S17" s="65"/>
     </row>
     <row r="18" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -6447,9 +7129,15 @@
       <c r="H18" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
+      <c r="I18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L18" s="37">
         <v>1</v>
       </c>
@@ -6457,14 +7145,20 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="38"/>
+      <c r="N18" s="37">
+        <v>51</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="38">
+        <v>0.68</v>
+      </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="37"/>
+        <v>34.68</v>
+      </c>
+      <c r="R18" s="83"/>
       <c r="S18" s="59"/>
     </row>
     <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -6473,53 +7167,53 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="G19" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="L19" s="73">
+      <c r="H19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" s="63">
         <v>1</v>
       </c>
       <c r="M19" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P19" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q19" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="R19" s="51"/>
+      <c r="N19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P19" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q19" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="R19" s="105"/>
       <c r="S19" s="59"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -6528,52 +7222,54 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="77" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="76" t="s">
+      <c r="C20" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="76" t="s">
+      <c r="E20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="J20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="K20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="L20" s="76">
-        <v>1</v>
-      </c>
-      <c r="M20" s="76">
+      <c r="G20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="66">
+        <v>1</v>
+      </c>
+      <c r="M20" s="66">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="O20" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78" t="s">
-        <v>189</v>
-      </c>
-      <c r="R20" s="76"/>
-      <c r="S20" s="75"/>
+      <c r="N20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="O20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20" s="110" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q20" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="R20" s="113"/>
+      <c r="S20" s="65"/>
     </row>
     <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -6600,7 +7296,7 @@
         <v>129</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J21" s="51" t="s">
         <v>147</v>
@@ -6618,17 +7314,17 @@
       <c r="N21" s="51">
         <v>55</v>
       </c>
-      <c r="O21" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P21" s="52">
+      <c r="O21" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P21" s="102">
         <v>7.0699999999999999E-2</v>
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="5">P21*N21</f>
         <v>3.8885000000000001</v>
       </c>
-      <c r="R21" s="51"/>
+      <c r="R21" s="105"/>
       <c r="S21" s="59"/>
     </row>
     <row r="22" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -6647,7 +7343,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>88</v>
@@ -6656,13 +7352,13 @@
         <v>130</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J22" s="37" t="s">
         <v>148</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -6672,19 +7368,19 @@
         <v>50</v>
       </c>
       <c r="N22" s="37">
-        <v>10</v>
-      </c>
-      <c r="O22" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P22" s="38">
+        <v>60</v>
+      </c>
+      <c r="O22" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P22" s="108">
         <v>5.6099999999999997E-2</v>
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0.56099999999999994</v>
-      </c>
-      <c r="R22" s="37"/>
+        <v>3.3659999999999997</v>
+      </c>
+      <c r="R22" s="83"/>
       <c r="S22" s="59"/>
     </row>
     <row r="23" spans="1:19" ht="72" x14ac:dyDescent="0.25">
@@ -6712,12 +7408,14 @@
         <v>131</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J23" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="51"/>
+      <c r="K23" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L23" s="51">
         <v>1</v>
       </c>
@@ -6726,19 +7424,19 @@
         <v>50</v>
       </c>
       <c r="N23" s="51">
-        <v>20</v>
-      </c>
-      <c r="O23" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P23" s="52">
+        <v>60</v>
+      </c>
+      <c r="O23" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P23" s="102">
         <v>3.3500000000000002E-2</v>
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="6">P23*N23</f>
-        <v>0.67</v>
-      </c>
-      <c r="R23" s="51"/>
+        <v>2.0100000000000002</v>
+      </c>
+      <c r="R23" s="105"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -6766,7 +7464,7 @@
         <v>125</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J24" s="37" t="s">
         <v>150</v>
@@ -6782,19 +7480,19 @@
         <v>250</v>
       </c>
       <c r="N24" s="37">
-        <v>100</v>
-      </c>
-      <c r="O24" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P24" s="38">
+        <v>300</v>
+      </c>
+      <c r="O24" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P24" s="108">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.08</v>
-      </c>
-      <c r="R24" s="37"/>
+        <v>0.24000000000000002</v>
+      </c>
+      <c r="R24" s="83"/>
       <c r="S24" s="59"/>
     </row>
     <row r="25" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -6822,7 +7520,7 @@
         <v>132</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J25" s="51" t="s">
         <v>151</v>
@@ -6840,17 +7538,17 @@
       <c r="N25" s="51">
         <v>100</v>
       </c>
-      <c r="O25" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P25" s="52">
+      <c r="O25" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P25" s="102">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="7">P25*N25</f>
         <v>0.08</v>
       </c>
-      <c r="R25" s="51"/>
+      <c r="R25" s="105"/>
       <c r="S25" s="59"/>
     </row>
     <row r="26" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -6878,7 +7576,7 @@
         <v>132</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J26" s="37" t="s">
         <v>152</v>
@@ -6896,17 +7594,17 @@
       <c r="N26" s="37">
         <v>100</v>
       </c>
-      <c r="O26" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P26" s="38">
+      <c r="O26" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P26" s="108">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="R26" s="37"/>
+      <c r="R26" s="83"/>
       <c r="S26" s="59"/>
     </row>
     <row r="27" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -6934,7 +7632,7 @@
         <v>132</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J27" s="51" t="s">
         <v>153</v>
@@ -6950,19 +7648,19 @@
         <v>100</v>
       </c>
       <c r="N27" s="51">
-        <v>50</v>
-      </c>
-      <c r="O27" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P27" s="52">
+        <v>150</v>
+      </c>
+      <c r="O27" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P27" s="102">
         <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="8">P27*N27</f>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="R27" s="51"/>
+        <v>0.69</v>
+      </c>
+      <c r="R27" s="105"/>
       <c r="S27" s="59"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -6990,7 +7688,7 @@
         <v>125</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J28" s="37" t="s">
         <v>154</v>
@@ -7006,19 +7704,19 @@
         <v>200</v>
       </c>
       <c r="N28" s="37">
-        <v>100</v>
-      </c>
-      <c r="O28" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P28" s="38">
+        <v>300</v>
+      </c>
+      <c r="O28" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P28" s="108">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.09</v>
-      </c>
-      <c r="R28" s="37"/>
+        <v>0.27</v>
+      </c>
+      <c r="R28" s="83"/>
       <c r="S28" s="59"/>
     </row>
     <row r="29" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
@@ -7046,13 +7744,13 @@
         <v>133</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J29" s="51" t="s">
         <v>155</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -7062,19 +7760,19 @@
         <v>50</v>
       </c>
       <c r="N29" s="51">
-        <v>10</v>
-      </c>
-      <c r="O29" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P29" s="52">
-        <v>0.2923</v>
+        <v>55</v>
+      </c>
+      <c r="O29" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P29" s="102">
+        <v>0.2429</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="9">P29*N29</f>
-        <v>2.923</v>
-      </c>
-      <c r="R29" s="51"/>
+        <v>13.359500000000001</v>
+      </c>
+      <c r="R29" s="105"/>
       <c r="S29" s="59"/>
     </row>
     <row r="30" spans="1:19" ht="36" x14ac:dyDescent="0.25">
@@ -7102,13 +7800,13 @@
         <v>134</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J30" s="37" t="s">
         <v>156</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -7118,19 +7816,19 @@
         <v>50</v>
       </c>
       <c r="N30" s="37">
-        <v>6</v>
-      </c>
-      <c r="O30" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P30" s="38">
-        <v>0.87819999999999998</v>
+        <v>51</v>
+      </c>
+      <c r="O30" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P30" s="108">
+        <v>0.5696</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>5.2691999999999997</v>
-      </c>
-      <c r="R30" s="37"/>
+        <v>29.049599999999998</v>
+      </c>
+      <c r="R30" s="83"/>
       <c r="S30" s="59"/>
     </row>
     <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7158,12 +7856,14 @@
         <v>135</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="K31" s="51"/>
+        <v>185</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L31" s="51">
         <v>1</v>
       </c>
@@ -7171,14 +7871,20 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="52"/>
+      <c r="N31" s="51">
+        <v>51</v>
+      </c>
+      <c r="O31" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="P31" s="102">
+        <v>2.5</v>
+      </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="10">P31*N31</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="51"/>
+        <v>127.5</v>
+      </c>
+      <c r="R31" s="105"/>
       <c r="S31" s="59"/>
     </row>
     <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7206,12 +7912,14 @@
         <v>136</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J32" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K32" s="37"/>
+      <c r="K32" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L32" s="37">
         <v>1</v>
       </c>
@@ -7220,19 +7928,19 @@
         <v>50</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
-      </c>
-      <c r="O32" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P32" s="38">
-        <v>7.9299999999999995E-2</v>
+        <v>55</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P32" s="108">
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>0.79299999999999993</v>
-      </c>
-      <c r="R32" s="37"/>
+        <v>3.52</v>
+      </c>
+      <c r="R32" s="83"/>
       <c r="S32" s="59"/>
     </row>
     <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7254,18 +7962,20 @@
         <v>95</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H33" s="51" t="s">
         <v>137</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="K33" s="51"/>
+        <v>182</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L33" s="51">
         <v>1</v>
       </c>
@@ -7274,19 +7984,19 @@
         <v>50</v>
       </c>
       <c r="N33" s="51">
-        <v>6</v>
-      </c>
-      <c r="O33" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P33" s="52">
-        <v>0.81779999999999997</v>
+        <v>51</v>
+      </c>
+      <c r="O33" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P33" s="102">
+        <v>0.60940000000000005</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="11">P33*N33</f>
-        <v>4.9067999999999996</v>
-      </c>
-      <c r="R33" s="51"/>
+        <v>31.079400000000003</v>
+      </c>
+      <c r="R33" s="105"/>
       <c r="S33" s="59"/>
     </row>
     <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7314,12 +8024,14 @@
         <v>136</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J34" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K34" s="37"/>
+      <c r="K34" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L34" s="37">
         <v>1</v>
       </c>
@@ -7328,19 +8040,19 @@
         <v>50</v>
       </c>
       <c r="N34" s="37">
-        <v>10</v>
-      </c>
-      <c r="O34" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P34" s="38">
-        <v>0.1444</v>
+        <v>55</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P34" s="108">
+        <v>0.11559999999999999</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.444</v>
-      </c>
-      <c r="R34" s="37"/>
+        <v>6.3579999999999997</v>
+      </c>
+      <c r="R34" s="83"/>
       <c r="S34" s="59"/>
     </row>
     <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7368,10 +8080,12 @@
         <v>138</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
+      <c r="K35" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L35" s="51">
         <v>1</v>
       </c>
@@ -7379,14 +8093,20 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="52"/>
+      <c r="N35" s="51">
+        <v>51</v>
+      </c>
+      <c r="O35" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="P35" s="102">
+        <v>12.754</v>
+      </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="12">P35*N35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="51"/>
+        <v>650.45399999999995</v>
+      </c>
+      <c r="R35" s="105"/>
       <c r="S35" s="59"/>
     </row>
     <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7414,12 +8134,14 @@
         <v>137</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J36" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="K36" s="37"/>
+      <c r="K36" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L36" s="37">
         <v>1</v>
       </c>
@@ -7428,19 +8150,19 @@
         <v>50</v>
       </c>
       <c r="N36" s="37">
-        <v>6</v>
-      </c>
-      <c r="O36" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P36" s="38">
-        <v>0.33260000000000001</v>
+        <v>51</v>
+      </c>
+      <c r="O36" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P36" s="108">
+        <v>0.2848</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>1.9956</v>
-      </c>
-      <c r="R36" s="37"/>
+        <v>14.524799999999999</v>
+      </c>
+      <c r="R36" s="83"/>
       <c r="S36" s="59"/>
     </row>
     <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7471,7 +8193,9 @@
       <c r="J37" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="K37" s="51"/>
+      <c r="K37" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
@@ -7480,19 +8204,19 @@
         <v>50</v>
       </c>
       <c r="N37" s="51">
-        <v>6</v>
-      </c>
-      <c r="O37" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P37" s="52">
-        <v>2.3832</v>
+        <v>51</v>
+      </c>
+      <c r="O37" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P37" s="102">
+        <v>2.1255000000000002</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="13">P37*N37</f>
-        <v>14.299199999999999</v>
-      </c>
-      <c r="R37" s="51"/>
+        <v>108.40050000000001</v>
+      </c>
+      <c r="R37" s="105"/>
       <c r="S37" s="59"/>
     </row>
     <row r="38" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7523,89 +8247,245 @@
       <c r="J38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="37"/>
+      <c r="K38" s="89" t="s">
+        <v>185</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
-      <c r="M38" s="37">
+      <c r="M38" s="89">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="89">
+        <v>51</v>
+      </c>
+      <c r="O38" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P38" s="100">
+        <v>1.2585</v>
+      </c>
+      <c r="Q38" s="52">
+        <f>P38*N38</f>
+        <v>64.183499999999995</v>
+      </c>
+      <c r="R38" s="80"/>
+      <c r="S38" s="59"/>
+    </row>
+    <row r="39" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="46">
+        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="83">
+        <v>1</v>
+      </c>
+      <c r="M39" s="91">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N39" s="91">
+        <v>51</v>
+      </c>
+      <c r="O39" s="84" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" s="101">
+        <v>3.29</v>
+      </c>
+      <c r="Q39" s="52">
+        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
+        <v>167.79</v>
+      </c>
+      <c r="R39" s="104"/>
+      <c r="S39" s="91"/>
+    </row>
+    <row r="40" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="46">
+        <f t="shared" si="14"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J40" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="51"/>
+      <c r="L40" s="83">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N40" s="51">
+        <v>51</v>
+      </c>
+      <c r="O40" s="87" t="s">
+        <v>208</v>
+      </c>
+      <c r="P40" s="102">
+        <v>3.15</v>
+      </c>
+      <c r="Q40" s="52">
+        <f t="shared" si="15"/>
+        <v>160.65</v>
+      </c>
+      <c r="R40" s="105"/>
+      <c r="S40" s="51"/>
+    </row>
+    <row r="41" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="46">
+        <f t="shared" si="14"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="37"/>
+      <c r="E41" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="37"/>
+      <c r="G41" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="39"/>
+      <c r="L41" s="83">
+        <v>1</v>
+      </c>
+      <c r="M41" s="92">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N41" s="39">
+        <v>1</v>
+      </c>
+      <c r="O41" s="87" t="s">
+        <v>209</v>
+      </c>
+      <c r="P41" s="103">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="Q41" s="52">
+        <f t="shared" si="15"/>
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R41" s="106"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="79"/>
+      <c r="P42" s="88"/>
+      <c r="Q42" s="90">
+        <f>SUM(Q10:Q38)</f>
+        <v>1126.4336000000001</v>
+      </c>
+      <c r="R42" s="74"/>
+      <c r="S42" s="75"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O38" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P38" s="38">
-        <v>1.6069</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>9.6414000000000009</v>
-      </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="39"/>
-    </row>
-    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="48">
-        <f>SUM(Q10:Q38)</f>
-        <v>79.651499999999999</v>
-      </c>
-      <c r="R39" s="64"/>
-      <c r="S39" s="65"/>
-    </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="O40" s="69"/>
-      <c r="P40" s="69"/>
-      <c r="Q40" s="49">
-        <f>Q39/5</f>
-        <v>15.930299999999999</v>
-      </c>
-      <c r="R40" s="66"/>
-      <c r="S40" s="67"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="49">
+        <f>Q42/50</f>
+        <v>22.528672</v>
+      </c>
+      <c r="R43" s="76"/>
+      <c r="S43" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S40"/>
-    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -7631,16 +8511,41 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
+    <hyperlink ref="O41" r:id="rId24"/>
+    <hyperlink ref="O40" r:id="rId25"/>
+    <hyperlink ref="O39" r:id="rId26"/>
+    <hyperlink ref="O35" r:id="rId27"/>
+    <hyperlink ref="O18" r:id="rId28" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId24"/>
+  <pageSetup orientation="portrait" r:id="rId29"/>
+  <drawing r:id="rId30"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -7653,15 +8558,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="71"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -7672,7 +8577,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -7697,7 +8602,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -7711,7 +8616,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="72"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -7722,7 +8627,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -7736,7 +8641,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="73"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -7761,7 +8666,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="73"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -7782,7 +8687,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="73"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -7803,7 +8708,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="73"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -7824,7 +8729,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="73"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -7862,29 +8767,29 @@
         <v>175</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="P9" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="R9" s="111" t="s">
         <v>179</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="P9" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>182</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+    </row>
+    <row r="10" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="95"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -7908,7 +8813,7 @@
         <v>125</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>141</v>
@@ -7920,27 +8825,27 @@
         <v>6</v>
       </c>
       <c r="M10" s="37">
-        <f>L10*5</f>
-        <v>30</v>
+        <f>L10*100</f>
+        <v>600</v>
       </c>
       <c r="N10" s="37">
-        <v>100</v>
-      </c>
-      <c r="O10" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P10" s="38">
+        <v>700</v>
+      </c>
+      <c r="O10" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P10" s="108">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>0.11</v>
-      </c>
-      <c r="R10" s="37"/>
-      <c r="S10" s="50"/>
-    </row>
-    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
+        <v>0.77</v>
+      </c>
+      <c r="R10" s="83"/>
+      <c r="S10" s="114"/>
+    </row>
+    <row r="11" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="95"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -7964,7 +8869,7 @@
         <v>126</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J11" s="51" t="s">
         <v>142</v>
@@ -7975,28 +8880,28 @@
       <c r="L11" s="51">
         <v>1</v>
       </c>
-      <c r="M11" s="51">
-        <f t="shared" ref="M11" si="1">L11*5</f>
-        <v>5</v>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M41" si="1">L11*100</f>
+        <v>100</v>
       </c>
       <c r="N11" s="51">
-        <v>50</v>
-      </c>
-      <c r="O11" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P11" s="52">
+        <v>150</v>
+      </c>
+      <c r="O11" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P11" s="102">
         <v>1.09E-2</v>
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="R11" s="51"/>
+        <v>1.635</v>
+      </c>
+      <c r="R11" s="105"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+    <row r="12" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="95"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -8013,17 +8918,17 @@
       <c r="F12" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="76" t="s">
+      <c r="G12" s="66" t="s">
         <v>104</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>125</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K12" s="37" t="s">
         <v>165</v>
@@ -8032,27 +8937,27 @@
         <v>1</v>
       </c>
       <c r="M12" s="37">
-        <f>L12*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N12" s="37">
-        <v>50</v>
-      </c>
-      <c r="O12" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P12" s="38">
+        <v>150</v>
+      </c>
+      <c r="O12" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P12" s="108">
         <v>1.35E-2</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="R12" s="37"/>
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="R12" s="83"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="95"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -8076,7 +8981,7 @@
         <v>125</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J13" s="51" t="s">
         <v>143</v>
@@ -8087,28 +8992,28 @@
       <c r="L13" s="51">
         <v>1</v>
       </c>
-      <c r="M13" s="51">
-        <f t="shared" ref="M13" si="3">L13*5</f>
-        <v>5</v>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N13" s="51">
-        <v>100</v>
-      </c>
-      <c r="O13" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P13" s="52">
+        <v>200</v>
+      </c>
+      <c r="O13" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P13" s="102">
         <v>5.3E-3</v>
       </c>
       <c r="Q13" s="52">
-        <f t="shared" ref="Q13" si="4">P13*N13</f>
-        <v>0.53</v>
-      </c>
-      <c r="R13" s="51"/>
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>1.06</v>
+      </c>
+      <c r="R13" s="105"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+    <row r="14" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="95"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -8132,7 +9037,7 @@
         <v>125</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>144</v>
@@ -8144,27 +9049,27 @@
         <v>1</v>
       </c>
       <c r="M14" s="37">
-        <f>L14*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N14" s="37">
-        <v>20</v>
-      </c>
-      <c r="O14" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P14" s="38">
+        <v>120</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P14" s="108">
         <v>3.44E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0.68799999999999994</v>
-      </c>
-      <c r="R14" s="37"/>
+        <v>4.1280000000000001</v>
+      </c>
+      <c r="R14" s="83"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+    <row r="15" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="95"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -8179,7 +9084,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G15" s="51" t="s">
         <v>82</v>
@@ -8188,7 +9093,7 @@
         <v>127</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J15" s="51" t="s">
         <v>145</v>
@@ -8199,28 +9104,28 @@
       <c r="L15" s="51">
         <v>1</v>
       </c>
-      <c r="M15" s="51">
-        <f t="shared" ref="M15" si="5">L15*5</f>
-        <v>5</v>
+      <c r="M15" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N15" s="51">
-        <v>6</v>
-      </c>
-      <c r="O15" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P15" s="52">
-        <v>0.5998</v>
+        <v>101</v>
+      </c>
+      <c r="O15" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P15" s="102">
+        <v>0.45979999999999999</v>
       </c>
       <c r="Q15" s="52">
-        <f t="shared" ref="Q15" si="6">P15*N15</f>
-        <v>3.5987999999999998</v>
-      </c>
-      <c r="R15" s="51"/>
+        <f t="shared" ref="Q15" si="4">P15*N15</f>
+        <v>46.439799999999998</v>
+      </c>
+      <c r="R15" s="105"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+    <row r="16" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="95"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -8244,7 +9149,7 @@
         <v>125</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>146</v>
@@ -8256,80 +9161,82 @@
         <v>1</v>
       </c>
       <c r="M16" s="37">
-        <f>L16*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N16" s="37">
-        <v>10</v>
-      </c>
-      <c r="O16" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P16" s="38">
-        <v>6.3100000000000003E-2</v>
+        <v>110</v>
+      </c>
+      <c r="O16" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P16" s="108">
+        <v>5.16E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>0.63100000000000001</v>
-      </c>
-      <c r="R16" s="37"/>
+        <v>5.6760000000000002</v>
+      </c>
+      <c r="R16" s="83"/>
       <c r="S16" s="59"/>
     </row>
-    <row r="17" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="17" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="95"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="G17" s="73" t="s">
+      <c r="F17" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="H17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73">
+      <c r="H17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="L17" s="63">
         <v>4</v>
       </c>
-      <c r="M17" s="73">
-        <f t="shared" ref="M17" si="7">L17*5</f>
-        <v>20</v>
-      </c>
-      <c r="N17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O17" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q17" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="R17" s="73"/>
-      <c r="S17" s="75"/>
-    </row>
-    <row r="18" spans="1:19" ht="84" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="N17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O17" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P17" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q17" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" s="112"/>
+      <c r="S17" s="65"/>
+    </row>
+    <row r="18" spans="1:19" s="96" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="95"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -8352,136 +9259,150 @@
       <c r="H18" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
+      <c r="I18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L18" s="37">
         <v>1</v>
       </c>
       <c r="M18" s="37">
-        <f>L18*5</f>
-        <v>5</v>
-      </c>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="38"/>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N18" s="37">
+        <v>101</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="38">
+        <v>0.68</v>
+      </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="37"/>
+        <v>68.680000000000007</v>
+      </c>
+      <c r="R18" s="83"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
+    <row r="19" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="95"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="73" t="s">
+      <c r="D19" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="73" t="s">
+      <c r="E19" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="G19" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="H19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="K19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="L19" s="73">
-        <v>1</v>
-      </c>
-      <c r="M19" s="73">
-        <f t="shared" ref="M19" si="8">L19*5</f>
-        <v>5</v>
-      </c>
-      <c r="N19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="O19" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="P19" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q19" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="R19" s="51"/>
+      <c r="H19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="I19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" s="63">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O19" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="P19" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q19" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="R19" s="105"/>
       <c r="S19" s="59"/>
     </row>
-    <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+    <row r="20" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="95"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="37" t="s">
+      <c r="E20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="K20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="L20" s="37">
+      <c r="G20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="I20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="K20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="L20" s="66">
         <v>1</v>
       </c>
       <c r="M20" s="37">
-        <f>L20*5</f>
-        <v>5</v>
-      </c>
-      <c r="N20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="O20" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="R20" s="37"/>
-      <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="O20" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20" s="110" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q20" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="R20" s="113"/>
+      <c r="S20" s="65"/>
+    </row>
+    <row r="21" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="95"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8505,7 +9426,7 @@
         <v>129</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J21" s="51" t="s">
         <v>147</v>
@@ -8516,28 +9437,28 @@
       <c r="L21" s="51">
         <v>1</v>
       </c>
-      <c r="M21" s="51">
-        <f t="shared" ref="M21" si="9">L21*5</f>
-        <v>5</v>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N21" s="51">
-        <v>10</v>
-      </c>
-      <c r="O21" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P21" s="52">
-        <v>8.4000000000000005E-2</v>
+        <v>105</v>
+      </c>
+      <c r="O21" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P21" s="102">
+        <v>7.0699999999999999E-2</v>
       </c>
       <c r="Q21" s="52">
-        <f t="shared" ref="Q21" si="10">P21*N21</f>
-        <v>0.84000000000000008</v>
-      </c>
-      <c r="R21" s="51"/>
+        <f t="shared" ref="Q21" si="5">P21*N21</f>
+        <v>7.4234999999999998</v>
+      </c>
+      <c r="R21" s="105"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" ht="132" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+    <row r="22" spans="1:19" s="96" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A22" s="95"/>
       <c r="B22" s="46">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
@@ -8552,7 +9473,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>88</v>
@@ -8561,39 +9482,39 @@
         <v>130</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J22" s="37" t="s">
         <v>148</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
       </c>
       <c r="M22" s="37">
-        <f>L22*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N22" s="37">
-        <v>10</v>
-      </c>
-      <c r="O22" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P22" s="38">
-        <v>5.6099999999999997E-2</v>
+        <v>110</v>
+      </c>
+      <c r="O22" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P22" s="108">
+        <v>4.5199999999999997E-2</v>
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0.56099999999999994</v>
-      </c>
-      <c r="R22" s="37"/>
+        <v>4.9719999999999995</v>
+      </c>
+      <c r="R22" s="83"/>
       <c r="S22" s="59"/>
     </row>
-    <row r="23" spans="1:19" ht="192" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+    <row r="23" spans="1:19" s="96" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="95"/>
       <c r="B23" s="47">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -8617,37 +9538,39 @@
         <v>131</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J23" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="51"/>
+      <c r="K23" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L23" s="51">
         <v>1</v>
       </c>
-      <c r="M23" s="51">
-        <f t="shared" ref="M23" si="11">L23*5</f>
-        <v>5</v>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N23" s="51">
-        <v>20</v>
-      </c>
-      <c r="O23" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P23" s="52">
+        <v>120</v>
+      </c>
+      <c r="O23" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P23" s="102">
         <v>3.3500000000000002E-2</v>
       </c>
       <c r="Q23" s="52">
-        <f t="shared" ref="Q23" si="12">P23*N23</f>
-        <v>0.67</v>
-      </c>
-      <c r="R23" s="51"/>
+        <f t="shared" ref="Q23" si="6">P23*N23</f>
+        <v>4.0200000000000005</v>
+      </c>
+      <c r="R23" s="105"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+    <row r="24" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="95"/>
       <c r="B24" s="46">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
@@ -8671,7 +9594,7 @@
         <v>125</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J24" s="37" t="s">
         <v>150</v>
@@ -8683,27 +9606,27 @@
         <v>5</v>
       </c>
       <c r="M24" s="37">
-        <f>L24*5</f>
-        <v>25</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N24" s="37">
-        <v>100</v>
-      </c>
-      <c r="O24" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P24" s="38">
+        <v>600</v>
+      </c>
+      <c r="O24" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P24" s="108">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.08</v>
-      </c>
-      <c r="R24" s="37"/>
+        <v>0.48000000000000004</v>
+      </c>
+      <c r="R24" s="83"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" ht="132" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
+    <row r="25" spans="1:19" s="96" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A25" s="95"/>
       <c r="B25" s="47">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -8727,7 +9650,7 @@
         <v>132</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J25" s="51" t="s">
         <v>151</v>
@@ -8738,28 +9661,28 @@
       <c r="L25" s="51">
         <v>1</v>
       </c>
-      <c r="M25" s="51">
-        <f t="shared" ref="M25" si="13">L25*5</f>
-        <v>5</v>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N25" s="51">
-        <v>100</v>
-      </c>
-      <c r="O25" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P25" s="52">
+        <v>200</v>
+      </c>
+      <c r="O25" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P25" s="102">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q25" s="52">
-        <f t="shared" ref="Q25" si="14">P25*N25</f>
-        <v>0.08</v>
-      </c>
-      <c r="R25" s="51"/>
+        <f t="shared" ref="Q25" si="7">P25*N25</f>
+        <v>0.16</v>
+      </c>
+      <c r="R25" s="105"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" ht="132" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+    <row r="26" spans="1:19" s="96" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A26" s="95"/>
       <c r="B26" s="46">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
@@ -8783,7 +9706,7 @@
         <v>132</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J26" s="37" t="s">
         <v>152</v>
@@ -8795,27 +9718,27 @@
         <v>1</v>
       </c>
       <c r="M26" s="37">
-        <f>L26*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N26" s="37">
-        <v>100</v>
-      </c>
-      <c r="O26" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P26" s="38">
+        <v>200</v>
+      </c>
+      <c r="O26" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P26" s="108">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R26" s="37"/>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R26" s="83"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" ht="120" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+    <row r="27" spans="1:19" s="96" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="95"/>
       <c r="B27" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -8839,7 +9762,7 @@
         <v>132</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J27" s="51" t="s">
         <v>153</v>
@@ -8850,28 +9773,28 @@
       <c r="L27" s="51">
         <v>2</v>
       </c>
-      <c r="M27" s="51">
-        <f t="shared" ref="M27" si="15">L27*5</f>
-        <v>10</v>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="N27" s="51">
-        <v>50</v>
-      </c>
-      <c r="O27" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P27" s="52">
+        <v>250</v>
+      </c>
+      <c r="O27" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P27" s="102">
         <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q27" s="52">
-        <f t="shared" ref="Q27" si="16">P27*N27</f>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="R27" s="51"/>
+        <f t="shared" ref="Q27" si="8">P27*N27</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="R27" s="105"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+    <row r="28" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="95"/>
       <c r="B28" s="46">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
@@ -8895,7 +9818,7 @@
         <v>125</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J28" s="37" t="s">
         <v>154</v>
@@ -8907,27 +9830,27 @@
         <v>4</v>
       </c>
       <c r="M28" s="37">
-        <f>L28*5</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>400</v>
       </c>
       <c r="N28" s="37">
-        <v>100</v>
-      </c>
-      <c r="O28" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P28" s="38">
+        <v>500</v>
+      </c>
+      <c r="O28" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P28" s="108">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.09</v>
-      </c>
-      <c r="R28" s="37"/>
+        <v>0.45</v>
+      </c>
+      <c r="R28" s="83"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+    <row r="29" spans="1:19" s="96" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="95"/>
       <c r="B29" s="47">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -8951,39 +9874,39 @@
         <v>133</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J29" s="51" t="s">
         <v>155</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
       </c>
-      <c r="M29" s="51">
-        <f t="shared" ref="M29" si="17">L29*5</f>
-        <v>5</v>
+      <c r="M29" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N29" s="51">
-        <v>10</v>
-      </c>
-      <c r="O29" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P29" s="52">
-        <v>0.2923</v>
+        <v>105</v>
+      </c>
+      <c r="O29" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P29" s="102">
+        <v>0.2429</v>
       </c>
       <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="18">P29*N29</f>
-        <v>2.923</v>
-      </c>
-      <c r="R29" s="51"/>
+        <f t="shared" ref="Q29" si="9">P29*N29</f>
+        <v>25.5045</v>
+      </c>
+      <c r="R29" s="105"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+    <row r="30" spans="1:19" s="96" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="95"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
@@ -9007,39 +9930,39 @@
         <v>134</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J30" s="37" t="s">
         <v>156</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
       </c>
       <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N30" s="37">
-        <v>6</v>
-      </c>
-      <c r="O30" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P30" s="38">
-        <v>0.87819999999999998</v>
+        <v>101</v>
+      </c>
+      <c r="O30" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P30" s="108">
+        <v>0.50119999999999998</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>5.2691999999999997</v>
-      </c>
-      <c r="R30" s="37"/>
+        <v>50.621199999999995</v>
+      </c>
+      <c r="R30" s="83"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+    <row r="31" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="95"/>
       <c r="B31" s="47">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9063,31 +9986,39 @@
         <v>135</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="K31" s="51"/>
+        <v>185</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L31" s="51">
         <v>1</v>
       </c>
-      <c r="M31" s="51">
-        <f t="shared" ref="M31" si="19">L31*5</f>
-        <v>5</v>
-      </c>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="52"/>
+      <c r="M31" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N31" s="51">
+        <v>101</v>
+      </c>
+      <c r="O31" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="P31" s="102">
+        <v>2.5</v>
+      </c>
       <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="20">P31*N31</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="51"/>
+        <f t="shared" ref="Q31" si="10">P31*N31</f>
+        <v>252.5</v>
+      </c>
+      <c r="R31" s="105"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
+    <row r="32" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="95"/>
       <c r="B32" s="46">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
@@ -9111,37 +10042,39 @@
         <v>136</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J32" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="K32" s="37"/>
+      <c r="K32" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L32" s="37">
         <v>1</v>
       </c>
       <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
-      </c>
-      <c r="O32" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P32" s="38">
-        <v>7.9299999999999995E-2</v>
+        <v>105</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P32" s="108">
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>0.79299999999999993</v>
-      </c>
-      <c r="R32" s="37"/>
+        <v>6.72</v>
+      </c>
+      <c r="R32" s="83"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+    <row r="33" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="95"/>
       <c r="B33" s="47">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -9159,43 +10092,45 @@
         <v>95</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H33" s="51" t="s">
         <v>137</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="K33" s="51"/>
+        <v>182</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L33" s="51">
         <v>1</v>
       </c>
-      <c r="M33" s="51">
-        <f t="shared" ref="M33" si="21">L33*5</f>
-        <v>5</v>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N33" s="51">
-        <v>6</v>
-      </c>
-      <c r="O33" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P33" s="52">
-        <v>0.81779999999999997</v>
+        <v>101</v>
+      </c>
+      <c r="O33" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P33" s="102">
+        <v>0.5091</v>
       </c>
       <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="22">P33*N33</f>
-        <v>4.9067999999999996</v>
-      </c>
-      <c r="R33" s="51"/>
+        <f t="shared" ref="Q33" si="11">P33*N33</f>
+        <v>51.4191</v>
+      </c>
+      <c r="R33" s="105"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
+    <row r="34" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="95"/>
       <c r="B34" s="46">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
@@ -9219,37 +10154,39 @@
         <v>136</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J34" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="K34" s="37"/>
+      <c r="K34" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L34" s="37">
         <v>1</v>
       </c>
       <c r="M34" s="37">
-        <f>L34*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N34" s="37">
-        <v>10</v>
-      </c>
-      <c r="O34" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P34" s="38">
-        <v>0.1444</v>
+        <v>105</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P34" s="108">
+        <v>0.11559999999999999</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.444</v>
-      </c>
-      <c r="R34" s="37"/>
+        <v>12.138</v>
+      </c>
+      <c r="R34" s="83"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
+    <row r="35" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="95"/>
       <c r="B35" s="47">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -9273,29 +10210,39 @@
         <v>138</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
+        <v>185</v>
+      </c>
+      <c r="J35" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="K35" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L35" s="51">
         <v>1</v>
       </c>
-      <c r="M35" s="51">
-        <f t="shared" ref="M35" si="23">L35*5</f>
-        <v>5</v>
-      </c>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="52"/>
+      <c r="M35" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N35" s="51">
+        <v>101</v>
+      </c>
+      <c r="O35" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="P35" s="102">
+        <v>10.477069999999999</v>
+      </c>
       <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="24">P35*N35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="51"/>
+        <f t="shared" ref="Q35" si="12">P35*N35</f>
+        <v>1058.18407</v>
+      </c>
+      <c r="R35" s="105"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
+    <row r="36" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="95"/>
       <c r="B36" s="46">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
@@ -9319,37 +10266,39 @@
         <v>137</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J36" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="K36" s="37"/>
+      <c r="K36" s="37" t="s">
+        <v>185</v>
+      </c>
       <c r="L36" s="37">
         <v>1</v>
       </c>
       <c r="M36" s="37">
-        <f>L36*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N36" s="37">
-        <v>6</v>
-      </c>
-      <c r="O36" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P36" s="38">
-        <v>0.33260000000000001</v>
+        <v>101</v>
+      </c>
+      <c r="O36" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P36" s="108">
+        <v>0.2848</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>1.9956</v>
-      </c>
-      <c r="R36" s="37"/>
+        <v>28.764800000000001</v>
+      </c>
+      <c r="R36" s="83"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
+    <row r="37" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="95"/>
       <c r="B37" s="47">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -9376,32 +10325,34 @@
       <c r="J37" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="K37" s="51"/>
+      <c r="K37" s="51" t="s">
+        <v>185</v>
+      </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
-      <c r="M37" s="51">
-        <f t="shared" ref="M37" si="25">L37*5</f>
-        <v>5</v>
+      <c r="M37" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="N37" s="51">
-        <v>6</v>
-      </c>
-      <c r="O37" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="P37" s="52">
-        <v>2.3832</v>
+        <v>101</v>
+      </c>
+      <c r="O37" s="61" t="s">
+        <v>187</v>
+      </c>
+      <c r="P37" s="102">
+        <v>2.073</v>
       </c>
       <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="26">P37*N37</f>
-        <v>14.299199999999999</v>
-      </c>
-      <c r="R37" s="51"/>
+        <f t="shared" ref="Q37" si="13">P37*N37</f>
+        <v>209.37299999999999</v>
+      </c>
+      <c r="R37" s="105"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
+    <row r="38" spans="1:19" s="96" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="95"/>
       <c r="B38" s="46">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
@@ -9428,89 +10379,257 @@
       <c r="J38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="37"/>
+      <c r="K38" s="89" t="s">
+        <v>185</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
       <c r="M38" s="37">
-        <f>L38*5</f>
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N38" s="89">
+        <v>101</v>
+      </c>
+      <c r="O38" s="60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P38" s="100">
+        <v>1.1185</v>
+      </c>
+      <c r="Q38" s="52">
+        <f>P38*N38</f>
+        <v>112.96850000000001</v>
+      </c>
+      <c r="R38" s="80"/>
+      <c r="S38" s="59"/>
+    </row>
+    <row r="39" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="95"/>
+      <c r="B39" s="46">
+        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G39" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="83">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N39" s="91">
+        <v>101</v>
+      </c>
+      <c r="O39" s="84" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" s="101">
+        <v>3.29</v>
+      </c>
+      <c r="Q39" s="52">
+        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
+        <v>332.29</v>
+      </c>
+      <c r="R39" s="104"/>
+      <c r="S39" s="91"/>
+    </row>
+    <row r="40" spans="1:19" s="96" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="95"/>
+      <c r="B40" s="46">
+        <f t="shared" si="14"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E40" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="82" t="s">
+        <v>185</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J40" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="51"/>
+      <c r="L40" s="83">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N40" s="51">
+        <v>101</v>
+      </c>
+      <c r="O40" s="115" t="s">
+        <v>208</v>
+      </c>
+      <c r="P40" s="102">
+        <v>3.15</v>
+      </c>
+      <c r="Q40" s="52">
+        <f t="shared" si="15"/>
+        <v>318.14999999999998</v>
+      </c>
+      <c r="R40" s="105"/>
+      <c r="S40" s="51"/>
+    </row>
+    <row r="41" spans="1:19" s="96" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="95"/>
+      <c r="B41" s="46">
+        <f t="shared" si="14"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E41" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G41" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="J41" s="85" t="s">
+        <v>185</v>
+      </c>
+      <c r="K41" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L41" s="83">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N41" s="39">
+        <v>1</v>
+      </c>
+      <c r="O41" s="115" t="s">
+        <v>209</v>
+      </c>
+      <c r="P41" s="103">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="Q41" s="52">
+        <f t="shared" si="15"/>
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R41" s="106"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="N38" s="37">
+      <c r="O42" s="79"/>
+      <c r="P42" s="88"/>
+      <c r="Q42" s="90">
+        <f>SUM(Q10:Q38)</f>
+        <v>1957.40247</v>
+      </c>
+      <c r="R42" s="74"/>
+      <c r="S42" s="75"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="O38" s="70" t="s">
-        <v>191</v>
-      </c>
-      <c r="P38" s="38">
-        <v>1.6069</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>9.6414000000000009</v>
-      </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="39"/>
-    </row>
-    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="44"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="45"/>
-      <c r="M39" s="45"/>
-      <c r="N39" s="68" t="s">
-        <v>5</v>
-      </c>
-      <c r="O39" s="69"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="48">
-        <f>SUM(Q10:Q38)</f>
-        <v>50.671000000000006</v>
-      </c>
-      <c r="R39" s="64"/>
-      <c r="S39" s="65"/>
-    </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="O40" s="69"/>
-      <c r="P40" s="69"/>
-      <c r="Q40" s="49">
-        <f>Q39/5</f>
-        <v>10.134200000000002</v>
-      </c>
-      <c r="R40" s="66"/>
-      <c r="S40" s="67"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="49">
+        <f>Q42/100</f>
+        <v>19.574024699999999</v>
+      </c>
+      <c r="R43" s="76"/>
+      <c r="S43" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S40"/>
-    <mergeCell ref="N40:P40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -9536,8 +10655,13 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
+    <hyperlink ref="O41" r:id="rId24"/>
+    <hyperlink ref="O40" r:id="rId25"/>
+    <hyperlink ref="O39" r:id="rId26"/>
+    <hyperlink ref="O35" r:id="rId27"/>
+    <hyperlink ref="O18" r:id="rId28" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
--- a/Design Files/BLE_product-v1.0/BOM/eSpark_BOM_BLE_product-v1.0.xlsx
+++ b/Design Files/BLE_product-v1.0/BOM/eSpark_BOM_BLE_product-v1.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="210">
   <si>
     <t>Component list</t>
   </si>
@@ -634,9 +634,6 @@
   </si>
   <si>
     <t>Peripherals</t>
-  </si>
-  <si>
-    <t>dc2.0*0.5mm USB Charger Cable Small Pin Charging Cord</t>
   </si>
   <si>
     <t>USB DC 2.0*0.5mm Charging Cable for Mini S530 Smallest Invisible Wireless Bluetooth Earbuds Earphones Headphones Headset</t>
@@ -656,18 +653,6 @@
   </si>
   <si>
     <t>Chipsmall</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -890,7 +875,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1176,34 +1161,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -1222,19 +1179,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1270,7 +1214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1461,6 +1405,90 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1493,115 +1521,13 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2107,7 +2033,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2141,15 +2067,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2199,7 +2125,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2224,7 +2150,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="73"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2249,7 +2175,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="73"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2270,7 +2196,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="73"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2291,7 +2217,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="73"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2312,7 +2238,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="73"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2464,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M41" si="1">L11*10</f>
+        <f t="shared" ref="M11:M40" si="1">L11*10</f>
         <v>10</v>
       </c>
       <c r="N11" s="51">
@@ -2816,8 +2742,8 @@
       <c r="R17" s="63"/>
       <c r="S17" s="65"/>
     </row>
-    <row r="18" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A18" s="95"/>
+    <row r="18" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="80"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -2860,7 +2786,7 @@
         <v>12</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P18" s="38">
         <v>0.68</v>
@@ -3586,7 +3512,7 @@
         <v>11</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P31" s="52">
         <v>2.7</v>
@@ -3810,7 +3736,7 @@
         <v>11</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P35" s="52">
         <v>18.221</v>
@@ -3986,25 +3912,25 @@
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="46">
-        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <f t="shared" ref="B39:B40" si="14">ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="81" t="s">
+      <c r="C39" s="71" t="s">
         <v>203</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="82" t="s">
+      <c r="E39" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="72" t="s">
         <v>185</v>
       </c>
       <c r="H39" s="37" t="s">
@@ -4013,55 +3939,55 @@
       <c r="I39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J39" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K39" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="L39" s="83">
+      <c r="J39" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="73">
         <v>1</v>
       </c>
       <c r="M39" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="51">
         <v>11</v>
       </c>
-      <c r="O39" s="97" t="s">
-        <v>208</v>
-      </c>
-      <c r="P39" s="93">
-        <v>3.46</v>
+      <c r="O39" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="P39" s="52">
+        <v>3.15</v>
       </c>
       <c r="Q39" s="38">
-        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
-        <v>38.06</v>
-      </c>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91"/>
-    </row>
-    <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q39:Q40" si="15">P39*N39</f>
+        <v>34.65</v>
+      </c>
+      <c r="R39" s="51"/>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="46">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="C40" s="81" t="s">
+      <c r="C40" s="71" t="s">
         <v>203</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E40" s="82" t="s">
+      <c r="E40" s="72" t="s">
         <v>205</v>
       </c>
       <c r="F40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G40" s="82" t="s">
-        <v>185</v>
+      <c r="G40" s="72" t="s">
+        <v>206</v>
       </c>
       <c r="H40" s="37" t="s">
         <v>185</v>
@@ -4069,150 +3995,94 @@
       <c r="I40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J40" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K40" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="L40" s="83">
+      <c r="J40" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L40" s="73">
         <v>1</v>
       </c>
       <c r="M40" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N40" s="51">
-        <v>11</v>
-      </c>
-      <c r="O40" s="98" t="s">
+      <c r="N40" s="39">
+        <v>1</v>
+      </c>
+      <c r="O40" s="83" t="s">
         <v>208</v>
       </c>
-      <c r="P40" s="52">
-        <v>3.15</v>
+      <c r="P40" s="79">
+        <v>33.950000000000003</v>
       </c>
       <c r="Q40" s="38">
         <f t="shared" si="15"/>
-        <v>34.65</v>
-      </c>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-    </row>
-    <row r="41" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R40" s="39"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="46">
-        <f t="shared" si="14"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41" s="82" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="G41" s="82" t="s">
-        <v>207</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="J41" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K41" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="L41" s="83">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N41" s="39">
-        <v>1</v>
-      </c>
-      <c r="O41" s="99" t="s">
-        <v>209</v>
-      </c>
-      <c r="P41" s="94">
-        <v>33.950000000000003</v>
-      </c>
-      <c r="Q41" s="38">
-        <f t="shared" si="15"/>
-        <v>33.950000000000003</v>
-      </c>
-      <c r="R41" s="39"/>
-      <c r="S41" s="39"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="106" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="107"/>
+      <c r="P41" s="107"/>
+      <c r="Q41" s="48">
+        <f>SUM(Q10:Q40)</f>
+        <v>387.37529999999992</v>
+      </c>
+      <c r="R41" s="102"/>
+      <c r="S41" s="103"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="79"/>
-      <c r="P42" s="79"/>
-      <c r="Q42" s="48">
-        <f>SUM(Q10:Q38)</f>
-        <v>318.77529999999996</v>
-      </c>
-      <c r="R42" s="74"/>
-      <c r="S42" s="75"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="78" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="79"/>
-      <c r="P43" s="79"/>
-      <c r="Q43" s="49">
-        <f>Q42/10</f>
-        <v>31.877529999999997</v>
-      </c>
-      <c r="R43" s="76"/>
-      <c r="S43" s="77"/>
+      <c r="O42" s="107"/>
+      <c r="P42" s="107"/>
+      <c r="Q42" s="49">
+        <f>Q41/10</f>
+        <v>38.737529999999992</v>
+      </c>
+      <c r="R42" s="104"/>
+      <c r="S42" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="R41:S42"/>
+    <mergeCell ref="N41:P41"/>
     <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -4240,19 +4110,18 @@
     <hyperlink ref="O12" r:id="rId23"/>
     <hyperlink ref="O18" r:id="rId24" location="nav-specification"/>
     <hyperlink ref="O35" r:id="rId25"/>
-    <hyperlink ref="O41" r:id="rId26"/>
-    <hyperlink ref="O40" r:id="rId27"/>
-    <hyperlink ref="O39" r:id="rId28"/>
+    <hyperlink ref="O40" r:id="rId26"/>
+    <hyperlink ref="O39" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
-  <drawing r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4286,15 +4155,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4344,7 +4213,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4369,7 +4238,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="73"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4394,7 +4263,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="73"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4415,7 +4284,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="73"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4436,7 +4305,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="73"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4457,7 +4326,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="73"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4609,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M41" si="1">L11*20</f>
+        <f t="shared" ref="M11:M40" si="1">L11*20</f>
         <v>20</v>
       </c>
       <c r="N11" s="51">
@@ -5005,7 +4874,7 @@
         <v>21</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P18" s="38">
         <v>0.68</v>
@@ -5727,7 +5596,7 @@
         <v>21</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P31" s="52">
         <v>2.7</v>
@@ -5951,7 +5820,7 @@
         <v>21</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P35" s="52">
         <v>18.221</v>
@@ -6131,25 +6000,25 @@
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="46">
-        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <f t="shared" ref="B39:B40" si="14">ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="81" t="s">
+      <c r="C39" s="71" t="s">
         <v>203</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="82" t="s">
+      <c r="E39" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="72" t="s">
         <v>185</v>
       </c>
       <c r="H39" s="37" t="s">
@@ -6158,55 +6027,53 @@
       <c r="I39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J39" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K39" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="L39" s="83">
+      <c r="J39" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="L39" s="73">
         <v>1</v>
       </c>
       <c r="M39" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="51">
         <v>21</v>
       </c>
-      <c r="O39" s="97" t="s">
-        <v>208</v>
-      </c>
-      <c r="P39" s="93">
-        <v>3.46</v>
+      <c r="O39" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="P39" s="52">
+        <v>3.15</v>
       </c>
       <c r="Q39" s="38">
-        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
-        <v>72.66</v>
-      </c>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91"/>
-    </row>
-    <row r="40" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q39:Q40" si="15">P39*N39</f>
+        <v>66.149999999999991</v>
+      </c>
+      <c r="R39" s="51"/>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="46">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="C40" s="81" t="s">
+      <c r="C40" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="E40" s="82" t="s">
+      <c r="D40" s="37"/>
+      <c r="E40" s="72" t="s">
         <v>205</v>
       </c>
       <c r="F40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G40" s="82" t="s">
-        <v>185</v>
+      <c r="G40" s="72" t="s">
+        <v>206</v>
       </c>
       <c r="H40" s="37" t="s">
         <v>185</v>
@@ -6214,148 +6081,94 @@
       <c r="I40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J40" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K40" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="L40" s="83">
+      <c r="J40" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L40" s="73">
         <v>1</v>
       </c>
       <c r="M40" s="37">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N40" s="51">
-        <v>21</v>
-      </c>
-      <c r="O40" s="98" t="s">
+      <c r="N40" s="39">
+        <v>1</v>
+      </c>
+      <c r="O40" s="83" t="s">
         <v>208</v>
       </c>
-      <c r="P40" s="52">
-        <v>3.15</v>
+      <c r="P40" s="79">
+        <v>33.950000000000003</v>
       </c>
       <c r="Q40" s="38">
         <f t="shared" si="15"/>
-        <v>66.149999999999991</v>
-      </c>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-    </row>
-    <row r="41" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R40" s="39"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="46">
-        <f t="shared" si="14"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="82" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="G41" s="82" t="s">
-        <v>207</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="J41" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K41" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="L41" s="83">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N41" s="39">
-        <v>1</v>
-      </c>
-      <c r="O41" s="99" t="s">
-        <v>209</v>
-      </c>
-      <c r="P41" s="94">
-        <v>33.950000000000003</v>
-      </c>
-      <c r="Q41" s="38">
-        <f t="shared" si="15"/>
-        <v>33.950000000000003</v>
-      </c>
-      <c r="R41" s="39"/>
-      <c r="S41" s="39"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="106" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="107"/>
+      <c r="P41" s="107"/>
+      <c r="Q41" s="48">
+        <f>SUM(Q10:Q40)</f>
+        <v>699.43190000000004</v>
+      </c>
+      <c r="R41" s="102"/>
+      <c r="S41" s="103"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="79"/>
-      <c r="P42" s="79"/>
-      <c r="Q42" s="48">
-        <f>SUM(Q10:Q38)</f>
-        <v>599.33190000000002</v>
-      </c>
-      <c r="R42" s="74"/>
-      <c r="S42" s="75"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="78" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="79"/>
-      <c r="P43" s="79"/>
-      <c r="Q43" s="49">
-        <f>Q42/20</f>
-        <v>29.966595000000002</v>
-      </c>
-      <c r="R43" s="76"/>
-      <c r="S43" s="77"/>
+      <c r="O42" s="107"/>
+      <c r="P42" s="107"/>
+      <c r="Q42" s="49">
+        <f>Q41/20</f>
+        <v>34.971595000000001</v>
+      </c>
+      <c r="R42" s="104"/>
+      <c r="S42" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S42"/>
     <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -6381,20 +6194,19 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
-    <hyperlink ref="O41" r:id="rId24"/>
-    <hyperlink ref="O40" r:id="rId25"/>
-    <hyperlink ref="O39" r:id="rId26"/>
-    <hyperlink ref="O35" r:id="rId27"/>
-    <hyperlink ref="O18" r:id="rId28" location="nav-specification"/>
+    <hyperlink ref="O40" r:id="rId24"/>
+    <hyperlink ref="O39" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O18" r:id="rId27" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId29"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -6428,15 +6240,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6486,7 +6298,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6511,7 +6323,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="73"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6536,7 +6348,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="73"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -6557,7 +6369,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="73"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -6578,7 +6390,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="73"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -6599,7 +6411,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="73"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6645,13 +6457,13 @@
       <c r="O9" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="P9" s="107" t="s">
+      <c r="P9" s="89" t="s">
         <v>201</v>
       </c>
       <c r="Q9" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="R9" s="111" t="s">
+      <c r="R9" s="93" t="s">
         <v>179</v>
       </c>
       <c r="S9" s="30" t="s">
@@ -6704,14 +6516,14 @@
       <c r="O10" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="90">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
         <v>0.44</v>
       </c>
-      <c r="R10" s="83"/>
+      <c r="R10" s="73"/>
       <c r="S10" s="50"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -6751,7 +6563,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M41" si="1">L11*50</f>
+        <f t="shared" ref="M11:M40" si="1">L11*50</f>
         <v>50</v>
       </c>
       <c r="N11" s="51">
@@ -6760,14 +6572,14 @@
       <c r="O11" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P11" s="102">
+      <c r="P11" s="85">
         <v>1.09E-2</v>
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>1.0900000000000001</v>
       </c>
-      <c r="R11" s="105"/>
+      <c r="R11" s="87"/>
       <c r="S11" s="51"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -6816,14 +6628,14 @@
       <c r="O12" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P12" s="108">
+      <c r="P12" s="90">
         <v>1.35E-2</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
         <v>1.35</v>
       </c>
-      <c r="R12" s="83"/>
+      <c r="R12" s="73"/>
       <c r="S12" s="59"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -6872,14 +6684,14 @@
       <c r="O13" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P13" s="102">
+      <c r="P13" s="85">
         <v>5.3E-3</v>
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
         <v>0.53</v>
       </c>
-      <c r="R13" s="105"/>
+      <c r="R13" s="87"/>
       <c r="S13" s="59"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -6928,14 +6740,14 @@
       <c r="O14" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P14" s="108">
+      <c r="P14" s="90">
         <v>3.44E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
         <v>2.0640000000000001</v>
       </c>
-      <c r="R14" s="83"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="59"/>
     </row>
     <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -6984,14 +6796,14 @@
       <c r="O15" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P15" s="102">
+      <c r="P15" s="85">
         <v>0.45979999999999999</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
         <v>23.4498</v>
       </c>
-      <c r="R15" s="105"/>
+      <c r="R15" s="87"/>
       <c r="S15" s="59"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -7040,14 +6852,14 @@
       <c r="O16" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P16" s="108">
+      <c r="P16" s="90">
         <v>6.3100000000000003E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
         <v>3.786</v>
       </c>
-      <c r="R16" s="83"/>
+      <c r="R16" s="73"/>
       <c r="S16" s="59"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -7096,13 +6908,13 @@
       <c r="O17" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="P17" s="109" t="s">
+      <c r="P17" s="91" t="s">
         <v>185</v>
       </c>
       <c r="Q17" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="R17" s="112"/>
+      <c r="R17" s="94"/>
       <c r="S17" s="65"/>
     </row>
     <row r="18" spans="1:19" ht="36" x14ac:dyDescent="0.25">
@@ -7149,7 +6961,7 @@
         <v>51</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P18" s="38">
         <v>0.68</v>
@@ -7158,7 +6970,7 @@
         <f>P18*N18</f>
         <v>34.68</v>
       </c>
-      <c r="R18" s="83"/>
+      <c r="R18" s="73"/>
       <c r="S18" s="59"/>
     </row>
     <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7207,13 +7019,13 @@
       <c r="O19" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="P19" s="109" t="s">
+      <c r="P19" s="91" t="s">
         <v>185</v>
       </c>
       <c r="Q19" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="R19" s="105"/>
+      <c r="R19" s="87"/>
       <c r="S19" s="59"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -7262,13 +7074,13 @@
       <c r="O20" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="P20" s="110" t="s">
+      <c r="P20" s="92" t="s">
         <v>185</v>
       </c>
       <c r="Q20" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="R20" s="113"/>
+      <c r="R20" s="95"/>
       <c r="S20" s="65"/>
     </row>
     <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7317,14 +7129,14 @@
       <c r="O21" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P21" s="102">
+      <c r="P21" s="85">
         <v>7.0699999999999999E-2</v>
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="5">P21*N21</f>
         <v>3.8885000000000001</v>
       </c>
-      <c r="R21" s="105"/>
+      <c r="R21" s="87"/>
       <c r="S21" s="59"/>
     </row>
     <row r="22" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -7373,14 +7185,14 @@
       <c r="O22" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P22" s="108">
+      <c r="P22" s="90">
         <v>5.6099999999999997E-2</v>
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
         <v>3.3659999999999997</v>
       </c>
-      <c r="R22" s="83"/>
+      <c r="R22" s="73"/>
       <c r="S22" s="59"/>
     </row>
     <row r="23" spans="1:19" ht="72" x14ac:dyDescent="0.25">
@@ -7429,14 +7241,14 @@
       <c r="O23" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P23" s="102">
+      <c r="P23" s="85">
         <v>3.3500000000000002E-2</v>
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="6">P23*N23</f>
         <v>2.0100000000000002</v>
       </c>
-      <c r="R23" s="105"/>
+      <c r="R23" s="87"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7485,14 +7297,14 @@
       <c r="O24" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P24" s="108">
+      <c r="P24" s="90">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
         <v>0.24000000000000002</v>
       </c>
-      <c r="R24" s="83"/>
+      <c r="R24" s="73"/>
       <c r="S24" s="59"/>
     </row>
     <row r="25" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -7541,14 +7353,14 @@
       <c r="O25" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P25" s="102">
+      <c r="P25" s="85">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="7">P25*N25</f>
         <v>0.08</v>
       </c>
-      <c r="R25" s="105"/>
+      <c r="R25" s="87"/>
       <c r="S25" s="59"/>
     </row>
     <row r="26" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -7597,14 +7409,14 @@
       <c r="O26" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P26" s="108">
+      <c r="P26" s="90">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="R26" s="83"/>
+      <c r="R26" s="73"/>
       <c r="S26" s="59"/>
     </row>
     <row r="27" spans="1:19" ht="48" x14ac:dyDescent="0.25">
@@ -7653,14 +7465,14 @@
       <c r="O27" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P27" s="102">
+      <c r="P27" s="85">
         <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="8">P27*N27</f>
         <v>0.69</v>
       </c>
-      <c r="R27" s="105"/>
+      <c r="R27" s="87"/>
       <c r="S27" s="59"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -7709,14 +7521,14 @@
       <c r="O28" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P28" s="108">
+      <c r="P28" s="90">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
         <v>0.27</v>
       </c>
-      <c r="R28" s="83"/>
+      <c r="R28" s="73"/>
       <c r="S28" s="59"/>
     </row>
     <row r="29" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
@@ -7765,14 +7577,14 @@
       <c r="O29" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P29" s="102">
+      <c r="P29" s="85">
         <v>0.2429</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="9">P29*N29</f>
         <v>13.359500000000001</v>
       </c>
-      <c r="R29" s="105"/>
+      <c r="R29" s="87"/>
       <c r="S29" s="59"/>
     </row>
     <row r="30" spans="1:19" ht="36" x14ac:dyDescent="0.25">
@@ -7821,14 +7633,14 @@
       <c r="O30" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P30" s="108">
+      <c r="P30" s="90">
         <v>0.5696</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
         <v>29.049599999999998</v>
       </c>
-      <c r="R30" s="83"/>
+      <c r="R30" s="73"/>
       <c r="S30" s="59"/>
     </row>
     <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7875,16 +7687,16 @@
         <v>51</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>210</v>
-      </c>
-      <c r="P31" s="102">
+        <v>209</v>
+      </c>
+      <c r="P31" s="85">
         <v>2.5</v>
       </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="10">P31*N31</f>
         <v>127.5</v>
       </c>
-      <c r="R31" s="105"/>
+      <c r="R31" s="87"/>
       <c r="S31" s="59"/>
     </row>
     <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7933,14 +7745,14 @@
       <c r="O32" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P32" s="108">
+      <c r="P32" s="90">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
         <v>3.52</v>
       </c>
-      <c r="R32" s="83"/>
+      <c r="R32" s="73"/>
       <c r="S32" s="59"/>
     </row>
     <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -7989,14 +7801,14 @@
       <c r="O33" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P33" s="102">
+      <c r="P33" s="85">
         <v>0.60940000000000005</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="11">P33*N33</f>
         <v>31.079400000000003</v>
       </c>
-      <c r="R33" s="105"/>
+      <c r="R33" s="87"/>
       <c r="S33" s="59"/>
     </row>
     <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -8045,14 +7857,14 @@
       <c r="O34" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P34" s="108">
+      <c r="P34" s="90">
         <v>0.11559999999999999</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
         <v>6.3579999999999997</v>
       </c>
-      <c r="R34" s="83"/>
+      <c r="R34" s="73"/>
       <c r="S34" s="59"/>
     </row>
     <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -8097,16 +7909,16 @@
         <v>51</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="P35" s="102">
+        <v>209</v>
+      </c>
+      <c r="P35" s="85">
         <v>12.754</v>
       </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="12">P35*N35</f>
         <v>650.45399999999995</v>
       </c>
-      <c r="R35" s="105"/>
+      <c r="R35" s="87"/>
       <c r="S35" s="59"/>
     </row>
     <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -8155,14 +7967,14 @@
       <c r="O36" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P36" s="108">
+      <c r="P36" s="90">
         <v>0.2848</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
         <v>14.524799999999999</v>
       </c>
-      <c r="R36" s="83"/>
+      <c r="R36" s="73"/>
       <c r="S36" s="59"/>
     </row>
     <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -8209,17 +8021,17 @@
       <c r="O37" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P37" s="102">
+      <c r="P37" s="85">
         <v>2.1255000000000002</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="13">P37*N37</f>
         <v>108.40050000000001</v>
       </c>
-      <c r="R37" s="105"/>
+      <c r="R37" s="87"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="46">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -8247,51 +8059,51 @@
       <c r="J38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="89" t="s">
+      <c r="K38" s="76" t="s">
         <v>185</v>
       </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
-      <c r="M38" s="89">
+      <c r="M38" s="76">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N38" s="89">
+      <c r="N38" s="76">
         <v>51</v>
       </c>
       <c r="O38" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P38" s="100">
+      <c r="P38" s="84">
         <v>1.2585</v>
       </c>
       <c r="Q38" s="52">
         <f>P38*N38</f>
         <v>64.183499999999995</v>
       </c>
-      <c r="R38" s="80"/>
+      <c r="R38" s="70"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="72" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="46">
-        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <f t="shared" ref="B39:B40" si="14">ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="81" t="s">
+      <c r="C39" s="71" t="s">
         <v>203</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="82" t="s">
+      <c r="E39" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="72" t="s">
         <v>185</v>
       </c>
       <c r="H39" s="37" t="s">
@@ -8300,192 +8112,136 @@
       <c r="I39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J39" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K39" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="L39" s="83">
-        <v>1</v>
-      </c>
-      <c r="M39" s="91">
+      <c r="J39" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="51"/>
+      <c r="L39" s="73">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="51">
         <v>51</v>
       </c>
-      <c r="O39" s="84" t="s">
-        <v>208</v>
-      </c>
-      <c r="P39" s="101">
-        <v>3.29</v>
+      <c r="O39" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="P39" s="85">
+        <v>3.15</v>
       </c>
       <c r="Q39" s="52">
-        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
-        <v>167.79</v>
-      </c>
-      <c r="R39" s="104"/>
-      <c r="S39" s="91"/>
-    </row>
-    <row r="40" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q39:Q40" si="15">P39*N39</f>
+        <v>160.65</v>
+      </c>
+      <c r="R39" s="87"/>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="46">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="C40" s="81" t="s">
+      <c r="C40" s="71" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="E40" s="82" t="s">
+      <c r="D40" s="37"/>
+      <c r="E40" s="72" t="s">
         <v>205</v>
       </c>
-      <c r="F40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="G40" s="82" t="s">
-        <v>185</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="J40" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K40" s="51"/>
-      <c r="L40" s="83">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
+      <c r="F40" s="37"/>
+      <c r="G40" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="74"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="73">
+        <v>1</v>
+      </c>
+      <c r="M40" s="78">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N40" s="51">
-        <v>51</v>
-      </c>
-      <c r="O40" s="87" t="s">
+      <c r="N40" s="39">
+        <v>1</v>
+      </c>
+      <c r="O40" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="P40" s="102">
-        <v>3.15</v>
+      <c r="P40" s="86">
+        <v>33.950000000000003</v>
       </c>
       <c r="Q40" s="52">
         <f t="shared" si="15"/>
-        <v>160.65</v>
-      </c>
-      <c r="R40" s="105"/>
-      <c r="S40" s="51"/>
-    </row>
-    <row r="41" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="R40" s="88"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="46">
-        <f t="shared" si="14"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="82" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="37"/>
-      <c r="G41" s="82" t="s">
-        <v>207</v>
-      </c>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="83">
-        <v>1</v>
-      </c>
-      <c r="M41" s="92">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N41" s="39">
-        <v>1</v>
-      </c>
-      <c r="O41" s="87" t="s">
-        <v>209</v>
-      </c>
-      <c r="P41" s="103">
-        <v>33.950000000000003</v>
-      </c>
-      <c r="Q41" s="52">
-        <f t="shared" si="15"/>
-        <v>33.950000000000003</v>
-      </c>
-      <c r="R41" s="106"/>
-      <c r="S41" s="39"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="108" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="107"/>
+      <c r="P41" s="109"/>
+      <c r="Q41" s="77">
+        <f>SUM(Q10:Q40)</f>
+        <v>1321.0336000000002</v>
+      </c>
+      <c r="R41" s="102"/>
+      <c r="S41" s="103"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="86" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="79"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="90">
-        <f>SUM(Q10:Q38)</f>
-        <v>1126.4336000000001</v>
-      </c>
-      <c r="R42" s="74"/>
-      <c r="S42" s="75"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="78" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="79"/>
-      <c r="P43" s="79"/>
-      <c r="Q43" s="49">
-        <f>Q42/50</f>
-        <v>22.528672</v>
-      </c>
-      <c r="R43" s="76"/>
-      <c r="S43" s="77"/>
+      <c r="O42" s="107"/>
+      <c r="P42" s="107"/>
+      <c r="Q42" s="49">
+        <f>Q41/50</f>
+        <v>26.420672000000003</v>
+      </c>
+      <c r="R42" s="104"/>
+      <c r="S42" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S42"/>
     <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -8511,21 +8267,20 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
-    <hyperlink ref="O41" r:id="rId24"/>
-    <hyperlink ref="O40" r:id="rId25"/>
-    <hyperlink ref="O39" r:id="rId26"/>
-    <hyperlink ref="O35" r:id="rId27"/>
-    <hyperlink ref="O18" r:id="rId28" location="nav-specification"/>
+    <hyperlink ref="O40" r:id="rId24"/>
+    <hyperlink ref="O39" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O18" r:id="rId27" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId29"/>
-  <drawing r:id="rId30"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -8558,15 +8313,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="99"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -8616,7 +8371,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="72"/>
+      <c r="S3" s="100"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -8641,7 +8396,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="73"/>
+      <c r="S4" s="101"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -8666,7 +8421,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="73"/>
+      <c r="S5" s="101"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -8687,7 +8442,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="73"/>
+      <c r="S6" s="101"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8708,7 +8463,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="73"/>
+      <c r="S7" s="101"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8729,7 +8484,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="73"/>
+      <c r="S8" s="101"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -8775,21 +8530,21 @@
       <c r="O9" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="P9" s="107" t="s">
+      <c r="P9" s="89" t="s">
         <v>201</v>
       </c>
       <c r="Q9" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="R9" s="111" t="s">
+      <c r="R9" s="93" t="s">
         <v>179</v>
       </c>
       <c r="S9" s="30" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="95"/>
+    <row r="10" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="80"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
@@ -8834,18 +8589,18 @@
       <c r="O10" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="90">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
         <v>0.77</v>
       </c>
-      <c r="R10" s="83"/>
-      <c r="S10" s="114"/>
-    </row>
-    <row r="11" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="95"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="96"/>
+    </row>
+    <row r="11" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="80"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -8881,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M41" si="1">L11*100</f>
+        <f t="shared" ref="M11:M40" si="1">L11*100</f>
         <v>100</v>
       </c>
       <c r="N11" s="51">
@@ -8890,18 +8645,18 @@
       <c r="O11" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P11" s="102">
+      <c r="P11" s="85">
         <v>1.09E-2</v>
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
         <v>1.635</v>
       </c>
-      <c r="R11" s="105"/>
+      <c r="R11" s="87"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95"/>
+    <row r="12" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="80"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -8946,18 +8701,18 @@
       <c r="O12" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P12" s="108">
+      <c r="P12" s="90">
         <v>1.35E-2</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
         <v>2.0249999999999999</v>
       </c>
-      <c r="R12" s="83"/>
+      <c r="R12" s="73"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="95"/>
+    <row r="13" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="80"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -9002,18 +8757,18 @@
       <c r="O13" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P13" s="102">
+      <c r="P13" s="85">
         <v>5.3E-3</v>
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
         <v>1.06</v>
       </c>
-      <c r="R13" s="105"/>
+      <c r="R13" s="87"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="95"/>
+    <row r="14" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="80"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -9058,18 +8813,18 @@
       <c r="O14" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P14" s="108">
+      <c r="P14" s="90">
         <v>3.44E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
         <v>4.1280000000000001</v>
       </c>
-      <c r="R14" s="83"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="95"/>
+    <row r="15" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="80"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9114,18 +8869,18 @@
       <c r="O15" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P15" s="102">
+      <c r="P15" s="85">
         <v>0.45979999999999999</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
         <v>46.439799999999998</v>
       </c>
-      <c r="R15" s="105"/>
+      <c r="R15" s="87"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="95"/>
+    <row r="16" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="80"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -9170,18 +8925,18 @@
       <c r="O16" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P16" s="108">
+      <c r="P16" s="90">
         <v>5.16E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
         <v>5.6760000000000002</v>
       </c>
-      <c r="R16" s="83"/>
+      <c r="R16" s="73"/>
       <c r="S16" s="59"/>
     </row>
-    <row r="17" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="95"/>
+    <row r="17" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="80"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9226,17 +8981,17 @@
       <c r="O17" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="P17" s="109" t="s">
+      <c r="P17" s="91" t="s">
         <v>185</v>
       </c>
       <c r="Q17" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="R17" s="112"/>
+      <c r="R17" s="94"/>
       <c r="S17" s="65"/>
     </row>
-    <row r="18" spans="1:19" s="96" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="95"/>
+    <row r="18" spans="1:19" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="80"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -9279,7 +9034,7 @@
         <v>101</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P18" s="38">
         <v>0.68</v>
@@ -9288,11 +9043,11 @@
         <f>P18*N18</f>
         <v>68.680000000000007</v>
       </c>
-      <c r="R18" s="83"/>
+      <c r="R18" s="73"/>
       <c r="S18" s="59"/>
     </row>
-    <row r="19" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="95"/>
+    <row r="19" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="80"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9337,17 +9092,17 @@
       <c r="O19" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="P19" s="109" t="s">
+      <c r="P19" s="91" t="s">
         <v>185</v>
       </c>
       <c r="Q19" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="R19" s="105"/>
+      <c r="R19" s="87"/>
       <c r="S19" s="59"/>
     </row>
-    <row r="20" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="95"/>
+    <row r="20" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="80"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -9392,17 +9147,17 @@
       <c r="O20" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="P20" s="110" t="s">
+      <c r="P20" s="92" t="s">
         <v>185</v>
       </c>
       <c r="Q20" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="R20" s="113"/>
+      <c r="R20" s="95"/>
       <c r="S20" s="65"/>
     </row>
-    <row r="21" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="95"/>
+    <row r="21" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="80"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9447,18 +9202,18 @@
       <c r="O21" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P21" s="102">
+      <c r="P21" s="85">
         <v>7.0699999999999999E-2</v>
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="5">P21*N21</f>
         <v>7.4234999999999998</v>
       </c>
-      <c r="R21" s="105"/>
+      <c r="R21" s="87"/>
       <c r="S21" s="59"/>
     </row>
-    <row r="22" spans="1:19" s="96" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A22" s="95"/>
+    <row r="22" spans="1:19" s="81" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A22" s="80"/>
       <c r="B22" s="46">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
@@ -9503,18 +9258,18 @@
       <c r="O22" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P22" s="108">
+      <c r="P22" s="90">
         <v>4.5199999999999997E-2</v>
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
         <v>4.9719999999999995</v>
       </c>
-      <c r="R22" s="83"/>
+      <c r="R22" s="73"/>
       <c r="S22" s="59"/>
     </row>
-    <row r="23" spans="1:19" s="96" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="95"/>
+    <row r="23" spans="1:19" s="81" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="80"/>
       <c r="B23" s="47">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -9559,18 +9314,18 @@
       <c r="O23" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P23" s="102">
+      <c r="P23" s="85">
         <v>3.3500000000000002E-2</v>
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="6">P23*N23</f>
         <v>4.0200000000000005</v>
       </c>
-      <c r="R23" s="105"/>
+      <c r="R23" s="87"/>
       <c r="S23" s="59"/>
     </row>
-    <row r="24" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="95"/>
+    <row r="24" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="80"/>
       <c r="B24" s="46">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
@@ -9615,18 +9370,18 @@
       <c r="O24" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P24" s="108">
+      <c r="P24" s="90">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
         <v>0.48000000000000004</v>
       </c>
-      <c r="R24" s="83"/>
+      <c r="R24" s="73"/>
       <c r="S24" s="59"/>
     </row>
-    <row r="25" spans="1:19" s="96" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A25" s="95"/>
+    <row r="25" spans="1:19" s="81" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A25" s="80"/>
       <c r="B25" s="47">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -9671,18 +9426,18 @@
       <c r="O25" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P25" s="102">
+      <c r="P25" s="85">
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="7">P25*N25</f>
         <v>0.16</v>
       </c>
-      <c r="R25" s="105"/>
+      <c r="R25" s="87"/>
       <c r="S25" s="59"/>
     </row>
-    <row r="26" spans="1:19" s="96" customFormat="1" ht="48" x14ac:dyDescent="0.25">
-      <c r="A26" s="95"/>
+    <row r="26" spans="1:19" s="81" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A26" s="80"/>
       <c r="B26" s="46">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
@@ -9727,18 +9482,18 @@
       <c r="O26" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P26" s="108">
+      <c r="P26" s="90">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R26" s="83"/>
+      <c r="R26" s="73"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" s="96" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A27" s="95"/>
+    <row r="27" spans="1:19" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A27" s="80"/>
       <c r="B27" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -9783,18 +9538,18 @@
       <c r="O27" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P27" s="102">
+      <c r="P27" s="85">
         <v>4.5999999999999999E-3</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="8">P27*N27</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="R27" s="105"/>
+      <c r="R27" s="87"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" s="96" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="95"/>
+    <row r="28" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="80"/>
       <c r="B28" s="46">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
@@ -9839,18 +9594,18 @@
       <c r="O28" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P28" s="108">
+      <c r="P28" s="90">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
         <v>0.45</v>
       </c>
-      <c r="R28" s="83"/>
+      <c r="R28" s="73"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" s="96" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="95"/>
+    <row r="29" spans="1:19" s="81" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="80"/>
       <c r="B29" s="47">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9895,18 +9650,18 @@
       <c r="O29" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P29" s="102">
+      <c r="P29" s="85">
         <v>0.2429</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="9">P29*N29</f>
         <v>25.5045</v>
       </c>
-      <c r="R29" s="105"/>
+      <c r="R29" s="87"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" s="96" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A30" s="95"/>
+    <row r="30" spans="1:19" s="81" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A30" s="80"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
@@ -9951,18 +9706,18 @@
       <c r="O30" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P30" s="108">
+      <c r="P30" s="90">
         <v>0.50119999999999998</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
         <v>50.621199999999995</v>
       </c>
-      <c r="R30" s="83"/>
+      <c r="R30" s="73"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="95"/>
+    <row r="31" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A31" s="80"/>
       <c r="B31" s="47">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -10005,20 +9760,20 @@
         <v>101</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>210</v>
-      </c>
-      <c r="P31" s="102">
+        <v>209</v>
+      </c>
+      <c r="P31" s="85">
         <v>2.5</v>
       </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="10">P31*N31</f>
         <v>252.5</v>
       </c>
-      <c r="R31" s="105"/>
+      <c r="R31" s="87"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="95"/>
+    <row r="32" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="80"/>
       <c r="B32" s="46">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
@@ -10063,18 +9818,18 @@
       <c r="O32" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P32" s="108">
+      <c r="P32" s="90">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
         <v>6.72</v>
       </c>
-      <c r="R32" s="83"/>
+      <c r="R32" s="73"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="95"/>
+    <row r="33" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="80"/>
       <c r="B33" s="47">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -10119,18 +9874,18 @@
       <c r="O33" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P33" s="102">
+      <c r="P33" s="85">
         <v>0.5091</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="11">P33*N33</f>
         <v>51.4191</v>
       </c>
-      <c r="R33" s="105"/>
+      <c r="R33" s="87"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="95"/>
+    <row r="34" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="80"/>
       <c r="B34" s="46">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
@@ -10175,18 +9930,18 @@
       <c r="O34" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P34" s="108">
+      <c r="P34" s="90">
         <v>0.11559999999999999</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
         <v>12.138</v>
       </c>
-      <c r="R34" s="83"/>
+      <c r="R34" s="73"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="95"/>
+    <row r="35" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="80"/>
       <c r="B35" s="47">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -10229,20 +9984,20 @@
         <v>101</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="P35" s="102">
+        <v>209</v>
+      </c>
+      <c r="P35" s="85">
         <v>10.477069999999999</v>
       </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="12">P35*N35</f>
         <v>1058.18407</v>
       </c>
-      <c r="R35" s="105"/>
+      <c r="R35" s="87"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A36" s="95"/>
+    <row r="36" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="80"/>
       <c r="B36" s="46">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
@@ -10287,18 +10042,18 @@
       <c r="O36" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P36" s="108">
+      <c r="P36" s="90">
         <v>0.2848</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
         <v>28.764800000000001</v>
       </c>
-      <c r="R36" s="83"/>
+      <c r="R36" s="73"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="95"/>
+    <row r="37" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="80"/>
       <c r="B37" s="47">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -10341,18 +10096,18 @@
       <c r="O37" s="61" t="s">
         <v>187</v>
       </c>
-      <c r="P37" s="102">
+      <c r="P37" s="85">
         <v>2.073</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="13">P37*N37</f>
         <v>209.37299999999999</v>
       </c>
-      <c r="R37" s="105"/>
+      <c r="R37" s="87"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" s="96" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="95"/>
+    <row r="38" spans="1:19" s="81" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A38" s="80"/>
       <c r="B38" s="46">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
@@ -10379,7 +10134,7 @@
       <c r="J38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="K38" s="89" t="s">
+      <c r="K38" s="76" t="s">
         <v>185</v>
       </c>
       <c r="L38" s="37">
@@ -10389,41 +10144,41 @@
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N38" s="89">
+      <c r="N38" s="76">
         <v>101</v>
       </c>
       <c r="O38" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="P38" s="100">
+      <c r="P38" s="84">
         <v>1.1185</v>
       </c>
       <c r="Q38" s="52">
         <f>P38*N38</f>
         <v>112.96850000000001</v>
       </c>
-      <c r="R38" s="80"/>
+      <c r="R38" s="70"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" s="96" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="95"/>
+    <row r="39" spans="1:19" s="81" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="80"/>
       <c r="B39" s="46">
-        <f t="shared" ref="B39:B41" si="14">ROW(B39) - ROW($B$9)</f>
+        <f t="shared" ref="B39:B40" si="14">ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="81" t="s">
+      <c r="C39" s="71" t="s">
         <v>203</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="82" t="s">
+      <c r="E39" s="72" t="s">
         <v>204</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G39" s="82" t="s">
+      <c r="G39" s="72" t="s">
         <v>185</v>
       </c>
       <c r="H39" s="37" t="s">
@@ -10432,55 +10187,53 @@
       <c r="I39" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J39" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K39" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="L39" s="83">
+      <c r="J39" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K39" s="51"/>
+      <c r="L39" s="73">
         <v>1</v>
       </c>
       <c r="M39" s="37">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="51">
         <v>101</v>
       </c>
-      <c r="O39" s="84" t="s">
-        <v>208</v>
-      </c>
-      <c r="P39" s="101">
-        <v>3.29</v>
+      <c r="O39" s="97" t="s">
+        <v>207</v>
+      </c>
+      <c r="P39" s="85">
+        <v>3.15</v>
       </c>
       <c r="Q39" s="52">
-        <f t="shared" ref="Q39:Q41" si="15">P39*N39</f>
-        <v>332.29</v>
-      </c>
-      <c r="R39" s="104"/>
-      <c r="S39" s="91"/>
-    </row>
-    <row r="40" spans="1:19" s="96" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A40" s="95"/>
+        <f t="shared" ref="Q39:Q40" si="15">P39*N39</f>
+        <v>318.14999999999998</v>
+      </c>
+      <c r="R39" s="87"/>
+      <c r="S39" s="51"/>
+    </row>
+    <row r="40" spans="1:19" s="81" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="80"/>
       <c r="B40" s="46">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="C40" s="81" t="s">
+      <c r="C40" s="71" t="s">
         <v>203</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="E40" s="82" t="s">
+      <c r="E40" s="72" t="s">
         <v>205</v>
       </c>
       <c r="F40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="G40" s="82" t="s">
-        <v>185</v>
+      <c r="G40" s="72" t="s">
+        <v>206</v>
       </c>
       <c r="H40" s="37" t="s">
         <v>185</v>
@@ -10488,146 +10241,92 @@
       <c r="I40" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="J40" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K40" s="51"/>
-      <c r="L40" s="83">
+      <c r="J40" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="K40" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="L40" s="73">
         <v>1</v>
       </c>
       <c r="M40" s="37">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N40" s="51">
-        <v>101</v>
-      </c>
-      <c r="O40" s="115" t="s">
+      <c r="N40" s="39">
+        <v>1</v>
+      </c>
+      <c r="O40" s="97" t="s">
         <v>208</v>
       </c>
-      <c r="P40" s="102">
-        <v>3.15</v>
+      <c r="P40" s="86">
+        <v>33.950000000000003</v>
       </c>
       <c r="Q40" s="52">
         <f t="shared" si="15"/>
-        <v>318.14999999999998</v>
-      </c>
-      <c r="R40" s="105"/>
-      <c r="S40" s="51"/>
-    </row>
-    <row r="41" spans="1:19" s="96" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="95"/>
-      <c r="B41" s="46">
-        <f t="shared" si="14"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41" s="82" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="G41" s="82" t="s">
-        <v>207</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="J41" s="85" t="s">
-        <v>185</v>
-      </c>
-      <c r="K41" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="L41" s="83">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N41" s="39">
-        <v>1</v>
-      </c>
-      <c r="O41" s="115" t="s">
-        <v>209</v>
-      </c>
-      <c r="P41" s="103">
         <v>33.950000000000003</v>
       </c>
-      <c r="Q41" s="52">
-        <f t="shared" si="15"/>
-        <v>33.950000000000003</v>
-      </c>
-      <c r="R41" s="106"/>
-      <c r="S41" s="39"/>
+      <c r="R40" s="88"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="108" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="107"/>
+      <c r="P41" s="109"/>
+      <c r="Q41" s="77">
+        <f>SUM(Q10:Q40)</f>
+        <v>2309.5024699999999</v>
+      </c>
+      <c r="R41" s="102"/>
+      <c r="S41" s="103"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="86" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="79"/>
-      <c r="P42" s="88"/>
-      <c r="Q42" s="90">
-        <f>SUM(Q10:Q38)</f>
-        <v>1957.40247</v>
-      </c>
-      <c r="R42" s="74"/>
-      <c r="S42" s="75"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="78" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="79"/>
-      <c r="P43" s="79"/>
-      <c r="Q43" s="49">
-        <f>Q42/100</f>
-        <v>19.574024699999999</v>
-      </c>
-      <c r="R43" s="76"/>
-      <c r="S43" s="77"/>
+      <c r="O42" s="107"/>
+      <c r="P42" s="107"/>
+      <c r="Q42" s="49">
+        <f>Q41/100</f>
+        <v>23.0950247</v>
+      </c>
+      <c r="R42" s="104"/>
+      <c r="S42" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S42"/>
     <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
   </mergeCells>
@@ -10655,13 +10354,12 @@
     <hyperlink ref="O37" r:id="rId21"/>
     <hyperlink ref="O38" r:id="rId22"/>
     <hyperlink ref="O12" r:id="rId23"/>
-    <hyperlink ref="O41" r:id="rId24"/>
-    <hyperlink ref="O40" r:id="rId25"/>
-    <hyperlink ref="O39" r:id="rId26"/>
-    <hyperlink ref="O35" r:id="rId27"/>
-    <hyperlink ref="O18" r:id="rId28" location="nav-specification"/>
+    <hyperlink ref="O40" r:id="rId24"/>
+    <hyperlink ref="O39" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O18" r:id="rId27" location="nav-specification"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId29"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>